--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1,311 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>UIFormId</t>
-  </si>
-  <si>
-    <t>MenuForm</t>
-  </si>
-  <si>
-    <t>主菜单</t>
-  </si>
-  <si>
-    <t>MainForm</t>
-  </si>
-  <si>
-    <t>游戏界面</t>
-  </si>
-  <si>
-    <t>SettingForm</t>
-  </si>
-  <si>
-    <t>设置界面</t>
-  </si>
-  <si>
-    <t>GameOver</t>
-  </si>
-  <si>
-    <t>结束界面</t>
-  </si>
-  <si>
-    <t>Entity.EntityId</t>
-  </si>
-  <si>
-    <t>Cat</t>
-  </si>
-  <si>
-    <t>猫猫</t>
-  </si>
-  <si>
-    <t>GanTan</t>
-  </si>
-  <si>
-    <t>感叹号</t>
-  </si>
-  <si>
-    <t>Anger</t>
-  </si>
-  <si>
-    <t>愤怒</t>
-  </si>
-  <si>
-    <t>LightningBall</t>
-  </si>
-  <si>
-    <t>闪电球</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -497,7 +363,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -509,6 +375,30 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -618,167 +508,190 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -834,11 +747,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1098,111 +1074,160 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="9.375" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5083333333333" customWidth="1"/>
-    <col min="9" max="9" width="12.8333333333333" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col width="19" customWidth="1" style="1" min="2" max="2"/>
+    <col width="20.875" customWidth="1" style="1" min="3" max="3"/>
+    <col width="14.125" customWidth="1" style="1" min="4" max="5"/>
+    <col width="9.375" customWidth="1" style="1" min="6" max="6"/>
+    <col width="5" customWidth="1" style="1" min="7" max="7"/>
+    <col width="18.5833333333333" customWidth="1" style="1" min="8" max="8"/>
+    <col width="12.8333333333333" customWidth="1" style="1" min="9" max="9"/>
+    <col width="12.125" customWidth="1" style="1" min="10" max="10"/>
+    <col width="15.125" customWidth="1" style="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>*items</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="5" t="n"/>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1"/>
+    <row r="3" ht="99" customHeight="1" s="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>枚举项是否唯一</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>枚举名</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n"/>
     </row>
-    <row r="4" spans="1:12">
-      <c r="B4" t="s">
-        <v>19</v>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UIFormId</t>
+        </is>
       </c>
       <c r="C4" t="b">
         <v>0</v>
@@ -1210,40 +1235,81 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>HeroSelectForm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>选人界面</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
+    <row r="5">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>HudForm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>战斗界面</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
+    <row r="6">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>GameOverForm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>结算界面</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="H7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" t="s">
-        <v>27</v>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Entity.EntityId</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Wukong</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>悟空</t>
+        </is>
       </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="B9" t="s">
-        <v>28</v>
+    <row r="8">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>HuaguoshanMonkey</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>花果山猴子</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Battle.DamageKind</t>
+        </is>
       </c>
       <c r="C9" t="b">
         <v>0</v>
@@ -1251,35 +1317,39 @@
       <c r="D9" t="b">
         <v>1</v>
       </c>
-      <c r="H9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" t="s">
-        <v>30</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="H10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" t="s">
-        <v>32</v>
+    <row r="10">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>魔法</t>
+        </is>
       </c>
     </row>
-    <row r="11" spans="1:12">
-      <c r="H11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="H12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" t="s">
-        <v>36</v>
+    <row r="11">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>真实</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1287,7 +1357,6 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1088,7 +1088,7 @@
     <col width="9.375" customWidth="1" style="1" min="6" max="6"/>
     <col width="5" customWidth="1" style="1" min="7" max="7"/>
     <col width="18.5833333333333" customWidth="1" style="1" min="8" max="8"/>
-    <col width="12.8333333333333" customWidth="1" style="1" min="9" max="9"/>
+    <col width="19.8333333333333" customWidth="1" style="1" min="9" max="9"/>
     <col width="12.125" customWidth="1" style="1" min="10" max="10"/>
     <col width="15.125" customWidth="1" style="1" min="11" max="11"/>
   </cols>
@@ -1350,6 +1350,122 @@
         <is>
           <t>真实</t>
         </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>WukongAttack2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>悟空挥棍2</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>WukongAttack1And3</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>悟空挥棍1/3</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>WukongAttack4</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>悟空挥棍4</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>WukongHurt</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>悟空受击语音</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>WukongDeath</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>悟空死亡语音</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>WukongImpact</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>悟空命中音(棍打中东西)</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1308,7 +1308,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Battle.DamageKind</t>
+          <t>Monster.MonsterRank</t>
         </is>
       </c>
       <c r="C9" t="b">
@@ -1319,43 +1319,52 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>物理</t>
-        </is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="H10" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>魔法</t>
-        </is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="H11" t="inlineStr">
         <is>
-          <t>Real</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>真实</t>
-        </is>
+          <t>首领</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sound.SoundId</t>
+          <t>Battle.DamageKind</t>
         </is>
       </c>
       <c r="C12" t="b">
@@ -1366,105 +1375,152 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
+          <t>物理</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="H13" t="inlineStr">
         <is>
-          <t>WukongAttack2</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>悟空挥棍2</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
+          <t>魔法</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="H14" t="inlineStr">
         <is>
-          <t>WukongAttack1And3</t>
+          <t>Real</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>悟空挥棍1/3</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
+          <t>真实</t>
+        </is>
       </c>
     </row>
     <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>WukongAttack4</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>悟空挥棍4</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="H16" t="inlineStr">
         <is>
-          <t>WukongHurt</t>
+          <t>WukongAttack2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>悟空受击语音</t>
+          <t>悟空挥棍2</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="H17" t="inlineStr">
         <is>
-          <t>WukongDeath</t>
+          <t>WukongAttack1And3</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>悟空死亡语音</t>
+          <t>悟空挥棍1/3</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="H18" t="inlineStr">
         <is>
+          <t>WukongAttack4</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>悟空挥棍4</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>WukongHurt</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>悟空受击语音</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>WukongDeath</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>悟空死亡语音</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" t="inlineStr">
+        <is>
           <t>WukongImpact</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>悟空命中音(棍打中东西)</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J21" t="n">
         <v>6</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1224,304 +1224,324 @@
       <c r="L3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>UIFormId</t>
         </is>
       </c>
-      <c r="C4" t="b">
+      <c r="C4" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>HeroSelectForm</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>选人界面</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>HudForm</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>战斗界面</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>GameOverForm</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>结算界面</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>Entity.EntityId</t>
         </is>
       </c>
-      <c r="C7" t="b">
+      <c r="C7" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D7" t="b">
+      <c r="D7" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>Wukong</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>悟空</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>HuaguoshanMonkey</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>花果山猴子</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>Monster.MonsterRank</t>
         </is>
       </c>
-      <c r="C9" t="b">
+      <c r="C9" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D9" t="b">
+      <c r="D9" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="0" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="0" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t>精英</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>首领</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>Battle.DamageKind</t>
         </is>
       </c>
-      <c r="C12" t="b">
+      <c r="C12" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D12" t="b">
+      <c r="D12" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>物理</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>Magic</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>魔法</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>Real</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>真实</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>Sound.SoundId</t>
         </is>
       </c>
-      <c r="C15" t="b">
+      <c r="C15" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D15" t="b">
+      <c r="D15" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>WukongAttack2</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t>悟空挥棍2</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>WukongAttack1And3</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t>悟空挥棍1/3</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="18">
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>WukongAttack4</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="0" t="inlineStr">
         <is>
           <t>悟空挥棍4</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="0" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="19">
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>WukongHurt</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="0" t="inlineStr">
         <is>
           <t>悟空受击语音</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="0" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="20">
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>WukongDeath</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
         <is>
           <t>悟空死亡语音</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="0" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="21">
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>WukongImpact</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="0" t="inlineStr">
         <is>
           <t>悟空命中音(棍打中东西)</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="0" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Level1Bgm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>花果山BGM</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>花果山关卡背景音乐</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1224,324 +1224,283 @@
       <c r="L3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>UIFormId</t>
         </is>
       </c>
-      <c r="C4" s="0" t="b">
+      <c r="C4" t="b">
         <v>0</v>
       </c>
-      <c r="D4" s="0" t="b">
+      <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="0" t="inlineStr">
-        <is>
-          <t>HeroSelectForm</t>
-        </is>
-      </c>
-      <c r="I4" s="0" t="inlineStr">
-        <is>
-          <t>选人界面</t>
-        </is>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="H5" s="0" t="inlineStr">
-        <is>
-          <t>HudForm</t>
-        </is>
-      </c>
-      <c r="I5" s="0" t="inlineStr">
-        <is>
-          <t>战斗界面</t>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Entity.EntityId</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Wukong</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>悟空</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="H6" s="0" t="inlineStr">
-        <is>
-          <t>GameOverForm</t>
-        </is>
-      </c>
-      <c r="I6" s="0" t="inlineStr">
-        <is>
-          <t>结算界面</t>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>HuaguoshanMonkey</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>花果山猴子</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>Entity.EntityId</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="b">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Monster.MonsterRank</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
         <v>0</v>
       </c>
-      <c r="D7" s="0" t="b">
+      <c r="D7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" s="0" t="inlineStr">
-        <is>
-          <t>Wukong</t>
-        </is>
-      </c>
-      <c r="I7" s="0" t="inlineStr">
-        <is>
-          <t>悟空</t>
-        </is>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="H8" s="0" t="inlineStr">
-        <is>
-          <t>HuaguoshanMonkey</t>
-        </is>
-      </c>
-      <c r="I8" s="0" t="inlineStr">
-        <is>
-          <t>花果山猴子</t>
-        </is>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>Monster.MonsterRank</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="b">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>首领</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Battle.DamageKind</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
         <v>0</v>
       </c>
-      <c r="D9" s="0" t="b">
+      <c r="D10" t="b">
         <v>1</v>
       </c>
-      <c r="H9" s="0" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I9" s="0" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="J9" s="0" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>魔法</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>真实</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="I10" s="0" t="inlineStr">
-        <is>
-          <t>精英</t>
-        </is>
-      </c>
-      <c r="J10" s="0" t="n">
+      <c r="D13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="H11" s="0" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
-      <c r="I11" s="0" t="inlineStr">
-        <is>
-          <t>首领</t>
-        </is>
-      </c>
-      <c r="J11" s="0" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>WukongAttack2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>悟空挥棍2</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>WukongAttack1And3</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>悟空挥棍1/3</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>Battle.DamageKind</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="I12" s="0" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="H13" s="0" t="inlineStr">
-        <is>
-          <t>Magic</t>
-        </is>
-      </c>
-      <c r="I13" s="0" t="inlineStr">
-        <is>
-          <t>魔法</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="H14" s="0" t="inlineStr">
-        <is>
-          <t>Real</t>
-        </is>
-      </c>
-      <c r="I14" s="0" t="inlineStr">
-        <is>
-          <t>真实</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t>Sound.SoundId</t>
-        </is>
-      </c>
-      <c r="C15" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="0" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I15" s="0" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="J15" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="16">
-      <c r="H16" s="0" t="inlineStr">
-        <is>
-          <t>WukongAttack2</t>
-        </is>
-      </c>
-      <c r="I16" s="0" t="inlineStr">
-        <is>
-          <t>悟空挥棍2</t>
-        </is>
-      </c>
-      <c r="J16" s="0" t="n">
-        <v>1</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>WukongAttack4</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>悟空挥棍4</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
-      <c r="H17" s="0" t="inlineStr">
-        <is>
-          <t>WukongAttack1And3</t>
-        </is>
-      </c>
-      <c r="I17" s="0" t="inlineStr">
-        <is>
-          <t>悟空挥棍1/3</t>
-        </is>
-      </c>
-      <c r="J17" s="0" t="n">
-        <v>2</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>WukongHurt</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>悟空受击语音</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
-      <c r="H18" s="0" t="inlineStr">
-        <is>
-          <t>WukongAttack4</t>
-        </is>
-      </c>
-      <c r="I18" s="0" t="inlineStr">
-        <is>
-          <t>悟空挥棍4</t>
-        </is>
-      </c>
-      <c r="J18" s="0" t="n">
-        <v>3</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>WukongDeath</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>悟空死亡语音</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
-      <c r="H19" s="0" t="inlineStr">
-        <is>
-          <t>WukongHurt</t>
-        </is>
-      </c>
-      <c r="I19" s="0" t="inlineStr">
-        <is>
-          <t>悟空受击语音</t>
-        </is>
-      </c>
-      <c r="J19" s="0" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="H20" s="0" t="inlineStr">
-        <is>
-          <t>WukongDeath</t>
-        </is>
-      </c>
-      <c r="I20" s="0" t="inlineStr">
-        <is>
-          <t>悟空死亡语音</t>
-        </is>
-      </c>
-      <c r="J20" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="H21" s="0" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>WukongImpact</t>
         </is>
       </c>
-      <c r="I21" s="0" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>悟空命中音(棍打中东西)</t>
         </is>
       </c>
-      <c r="J21" s="0" t="n">
+      <c r="J19" t="n">
         <v>6</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Level1Bgm</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>花果山BGM</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>7</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>花果山关卡背景音乐</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1224,283 +1224,365 @@
       <c r="L3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>UIFormId</t>
         </is>
       </c>
-      <c r="C4" t="b">
+      <c r="C4" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Entity.EntityId</t>
         </is>
       </c>
-      <c r="C5" t="b">
+      <c r="C5" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D5" t="b">
+      <c r="D5" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>Wukong</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>悟空</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>HuaguoshanMonkey</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>花果山猴子</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>Monster.MonsterRank</t>
         </is>
       </c>
-      <c r="C7" t="b">
+      <c r="C7" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D7" t="b">
+      <c r="D7" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>精英</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="0" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>首领</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>Battle.DamageKind</t>
         </is>
       </c>
-      <c r="C10" t="b">
+      <c r="C10" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D10" t="b">
+      <c r="D10" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="0" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t>物理</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>Magic</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>魔法</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>Real</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>真实</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>Sound.SoundId</t>
         </is>
       </c>
-      <c r="C13" t="b">
+      <c r="C13" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>WukongAttack2</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>悟空挥棍2</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>WukongAttack1And3</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>悟空挥棍1/3</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16">
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>WukongAttack4</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t>悟空挥棍4</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="0" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="17">
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>WukongHurt</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t>悟空受击语音</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="0" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="18">
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>WukongDeath</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="0" t="inlineStr">
         <is>
           <t>悟空死亡语音</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="0" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="19">
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>WukongImpact</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="0" t="inlineStr">
         <is>
           <t>悟空命中音(棍打中东西)</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="0" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Level.StageActivation</t>
+        </is>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>OnEnter</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>进入关卡</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>触发器</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>OnClear</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>前阶段清除</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Level.StageClearPolicy</t>
+        </is>
+      </c>
+      <c r="C23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>KillAll</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>清除全部活跃怪物</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1504,85 +1504,44 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>Level.StageActivation</t>
         </is>
       </c>
-      <c r="C20" t="b">
+      <c r="C20" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D20" t="b">
+      <c r="D20" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>OnEnter</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>进入关卡</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>CameraArrived</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>相机抵达阶段右界</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>触发器</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>特殊区域激活</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>OnClear</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>前阶段清除</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Level.StageClearPolicy</t>
-        </is>
-      </c>
-      <c r="C23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>KillAll</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>清除全部活跃怪物</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1285,262 +1285,277 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="0" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DemonMonkey</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>妖猴</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>Monster.MonsterRank</t>
         </is>
       </c>
-      <c r="C7" s="0" t="b">
+      <c r="C8" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D7" s="0" t="b">
+      <c r="D8" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H7" s="0" t="inlineStr">
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I7" s="0" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J8" s="0" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="H8" s="0" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="I8" s="0" t="inlineStr">
-        <is>
-          <t>精英</t>
-        </is>
-      </c>
-      <c r="J8" s="0" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="H9" s="0" t="inlineStr">
         <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="I9" s="0" t="inlineStr">
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t>首领</t>
         </is>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="J10" s="0" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="0" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>Battle.DamageKind</t>
         </is>
       </c>
-      <c r="C10" s="0" t="b">
+      <c r="C11" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D10" s="0" t="b">
+      <c r="D11" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H10" s="0" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="I10" s="0" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>物理</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="H11" s="0" t="inlineStr">
-        <is>
-          <t>Magic</t>
-        </is>
-      </c>
-      <c r="I11" s="0" t="inlineStr">
-        <is>
-          <t>魔法</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="H12" s="0" t="inlineStr">
         <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>魔法</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" s="0" t="inlineStr">
+        <is>
           <t>Real</t>
         </is>
       </c>
-      <c r="I12" s="0" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>真实</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="0" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>Sound.SoundId</t>
         </is>
       </c>
-      <c r="C13" s="0" t="b">
+      <c r="C14" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D13" s="0" t="b">
+      <c r="D14" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H13" s="0" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I13" s="0" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J13" s="0" t="n">
+      <c r="J14" s="0" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="H14" s="0" t="inlineStr">
-        <is>
-          <t>WukongAttack2</t>
-        </is>
-      </c>
-      <c r="I14" s="0" t="inlineStr">
-        <is>
-          <t>悟空挥棍2</t>
-        </is>
-      </c>
-      <c r="J14" s="0" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>WukongAttack1And3</t>
+          <t>WukongAttack2</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t>悟空挥棍1/3</t>
+          <t>悟空挥棍2</t>
         </is>
       </c>
       <c r="J15" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>WukongAttack4</t>
+          <t>WukongAttack1And3</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t>悟空挥棍4</t>
+          <t>悟空挥棍1/3</t>
         </is>
       </c>
       <c r="J16" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>WukongHurt</t>
+          <t>WukongAttack4</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t>悟空受击语音</t>
+          <t>悟空挥棍4</t>
         </is>
       </c>
       <c r="J17" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>WukongDeath</t>
+          <t>WukongHurt</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t>悟空死亡语音</t>
+          <t>悟空受击语音</t>
         </is>
       </c>
       <c r="J18" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="H19" s="0" t="inlineStr">
         <is>
+          <t>WukongDeath</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>悟空死亡语音</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" s="0" t="inlineStr">
+        <is>
           <t>WukongImpact</t>
         </is>
       </c>
-      <c r="I19" s="0" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
         <is>
           <t>悟空命中音(棍打中东西)</t>
         </is>
       </c>
-      <c r="J19" s="0" t="n">
+      <c r="J20" s="0" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="0" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>Level.StageActivation</t>
         </is>
       </c>
-      <c r="C20" s="0" t="b">
+      <c r="C21" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D20" s="0" t="b">
+      <c r="D21" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H20" s="0" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>CameraArrived</t>
         </is>
       </c>
-      <c r="I20" s="0" t="inlineStr">
+      <c r="I21" s="0" t="inlineStr">
         <is>
           <t>相机抵达阶段右界</t>
         </is>
       </c>
-      <c r="J20" s="0" t="n">
+      <c r="J21" s="0" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="H21" s="0" t="inlineStr">
+    <row r="22">
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="I21" s="0" t="inlineStr">
+      <c r="I22" s="0" t="inlineStr">
         <is>
           <t>特殊区域激活</t>
         </is>
       </c>
-      <c r="J21" s="0" t="n">
+      <c r="J22" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1250,312 +1250,327 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="0" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>BattleHud</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>战斗HUD</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Entity.EntityId</t>
         </is>
       </c>
-      <c r="C5" s="0" t="b">
+      <c r="C6" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D5" s="0" t="b">
+      <c r="D6" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H5" s="0" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>Wukong</t>
         </is>
       </c>
-      <c r="I5" s="0" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>悟空</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="H6" s="0" t="inlineStr">
+    <row r="7">
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>HuaguoshanMonkey</t>
         </is>
       </c>
-      <c r="I6" s="0" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>花果山猴子</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="H7" t="inlineStr">
+    <row r="8">
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>DemonMonkey</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>妖猴</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" s="0" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="0" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>Monster.MonsterRank</t>
         </is>
       </c>
-      <c r="C8" s="0" t="b">
+      <c r="C9" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D8" s="0" t="b">
+      <c r="D9" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H8" s="0" t="inlineStr">
+      <c r="H9" s="0" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I8" s="0" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J9" s="0" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="H9" s="0" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="I9" s="0" t="inlineStr">
-        <is>
-          <t>精英</t>
-        </is>
-      </c>
-      <c r="J9" s="0" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="H10" s="0" t="inlineStr">
         <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" s="0" t="inlineStr">
+        <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="I10" s="0" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>首领</t>
         </is>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="J11" s="0" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="0" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>Battle.DamageKind</t>
         </is>
       </c>
-      <c r="C11" s="0" t="b">
+      <c r="C12" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D11" s="0" t="b">
+      <c r="D12" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H11" s="0" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="I11" s="0" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>物理</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t>Magic</t>
-        </is>
-      </c>
-      <c r="I12" s="0" t="inlineStr">
-        <is>
-          <t>魔法</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="H13" s="0" t="inlineStr">
         <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>魔法</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" s="0" t="inlineStr">
+        <is>
           <t>Real</t>
         </is>
       </c>
-      <c r="I13" s="0" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>真实</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="0" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>Sound.SoundId</t>
         </is>
       </c>
-      <c r="C14" s="0" t="b">
+      <c r="C15" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D14" s="0" t="b">
+      <c r="D15" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="0" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I14" s="0" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J14" s="0" t="n">
+      <c r="J15" s="0" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="H15" s="0" t="inlineStr">
-        <is>
-          <t>WukongAttack2</t>
-        </is>
-      </c>
-      <c r="I15" s="0" t="inlineStr">
-        <is>
-          <t>悟空挥棍2</t>
-        </is>
-      </c>
-      <c r="J15" s="0" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>WukongAttack1And3</t>
+          <t>WukongAttack2</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t>悟空挥棍1/3</t>
+          <t>悟空挥棍2</t>
         </is>
       </c>
       <c r="J16" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>WukongAttack4</t>
+          <t>WukongAttack1And3</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t>悟空挥棍4</t>
+          <t>悟空挥棍1/3</t>
         </is>
       </c>
       <c r="J17" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>WukongHurt</t>
+          <t>WukongAttack4</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t>悟空受击语音</t>
+          <t>悟空挥棍4</t>
         </is>
       </c>
       <c r="J18" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t>WukongDeath</t>
+          <t>WukongHurt</t>
         </is>
       </c>
       <c r="I19" s="0" t="inlineStr">
         <is>
-          <t>悟空死亡语音</t>
+          <t>悟空受击语音</t>
         </is>
       </c>
       <c r="J19" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="H20" s="0" t="inlineStr">
         <is>
+          <t>WukongDeath</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>悟空死亡语音</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" s="0" t="inlineStr">
+        <is>
           <t>WukongImpact</t>
         </is>
       </c>
-      <c r="I20" s="0" t="inlineStr">
+      <c r="I21" s="0" t="inlineStr">
         <is>
           <t>悟空命中音(棍打中东西)</t>
         </is>
       </c>
-      <c r="J20" s="0" t="n">
+      <c r="J21" s="0" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="0" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>Level.StageActivation</t>
         </is>
       </c>
-      <c r="C21" s="0" t="b">
+      <c r="C22" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D21" s="0" t="b">
+      <c r="D22" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H21" s="0" t="inlineStr">
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>CameraArrived</t>
         </is>
       </c>
-      <c r="I21" s="0" t="inlineStr">
+      <c r="I22" s="0" t="inlineStr">
         <is>
           <t>相机抵达阶段右界</t>
         </is>
       </c>
-      <c r="J21" s="0" t="n">
+      <c r="J22" s="0" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="H22" s="0" t="inlineStr">
+    <row r="23">
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="I22" s="0" t="inlineStr">
+      <c r="I23" s="0" t="inlineStr">
         <is>
           <t>特殊区域激活</t>
         </is>
       </c>
-      <c r="J22" s="0" t="n">
+      <c r="J23" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1250,17 +1250,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>BattleHud</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>战斗HUD</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1572,6 +1572,313 @@
       </c>
       <c r="J23" s="0" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stat.StatType</t>
+        </is>
+      </c>
+      <c r="C24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>MaxHp</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>生命上限</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>MaxMp</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>魔法上限</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>物防</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Mdef</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>魔防</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>暴击</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>闪避</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Lucky</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>幸运(加暴击倍率)</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>韧性(减对方幸运)</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Htarget</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>命中(减对方闪避)</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>CritReduce</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>暴击抵抗</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Ar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>破甲(减对方物防)</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sp</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>破魔(减对方魔防)</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Vampirism</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>吸血(百分点,伤害转生命)</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>HpRegen</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>每秒回血</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>MpRegen</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>每秒回蓝</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Stat.StatModifierKind</t>
+        </is>
+      </c>
+      <c r="C40" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>固定值</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>PercentAdd</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>同类百分比相加</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PercentMult</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>独立百分比相乘</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1265,619 +1265,754 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>Entity.EntityId</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t>Wukong</t>
+          <t>StartForm</t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t>悟空</t>
-        </is>
+          <t>开始界面</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>HuaguoshanMonkey</t>
+          <t>CharacterForm</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>花果山猴子</t>
-        </is>
+          <t>选角界面</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t>MapForm</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t>妖猴</t>
+          <t>地图界面</t>
         </is>
       </c>
       <c r="J8" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>Monster.MonsterRank</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>SettingsForm</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>设置界面</t>
         </is>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>SaveForm</t>
         </is>
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t>精英</t>
+          <t>存档选择</t>
         </is>
       </c>
       <c r="J10" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Entity.EntityId</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="0" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11">
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Wukong</t>
         </is>
       </c>
       <c r="I11" s="0" t="inlineStr">
         <is>
-          <t>首领</t>
-        </is>
-      </c>
-      <c r="J11" s="0" t="n">
-        <v>2</v>
+          <t>悟空</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>Battle.DamageKind</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>HuaguoshanMonkey</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t>物理</t>
+          <t>花果山猴子</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>DemonMonkey</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t>魔法</t>
-        </is>
+          <t>妖猴</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Monster.MonsterRank</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="0" t="b">
+        <v>1</v>
+      </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>Real</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t>真实</t>
-        </is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t>Sound.SoundId</t>
-        </is>
-      </c>
-      <c r="C15" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" s="0" t="b">
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="n">
         <v>1</v>
-      </c>
-      <c r="H15" s="0" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I15" s="0" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="J15" s="0" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>WukongAttack2</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t>悟空挥棍2</t>
+          <t>首领</t>
         </is>
       </c>
       <c r="J16" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Battle.DamageKind</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="0" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17">
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>WukongAttack1And3</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t>悟空挥棍1/3</t>
-        </is>
-      </c>
-      <c r="J17" s="0" t="n">
-        <v>2</v>
+          <t>物理</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>WukongAttack4</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t>悟空挥棍4</t>
-        </is>
-      </c>
-      <c r="J18" s="0" t="n">
-        <v>3</v>
+          <t>魔法</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t>WukongHurt</t>
+          <t>Real</t>
         </is>
       </c>
       <c r="I19" s="0" t="inlineStr">
         <is>
-          <t>悟空受击语音</t>
-        </is>
-      </c>
-      <c r="J19" s="0" t="n">
-        <v>4</v>
+          <t>真实</t>
+        </is>
       </c>
     </row>
     <row r="20">
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="0" t="b">
+        <v>1</v>
+      </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t>WukongDeath</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t>悟空死亡语音</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J20" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t>WukongImpact</t>
+          <t>WukongAttack2</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>悟空命中音(棍打中东西)</t>
+          <t>悟空挥棍2</t>
         </is>
       </c>
       <c r="J21" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t>Level.StageActivation</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>CameraArrived</t>
+          <t>WukongAttack1And3</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t>相机抵达阶段右界</t>
+          <t>悟空挥棍1/3</t>
         </is>
       </c>
       <c r="J22" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="H23" s="0" t="inlineStr">
         <is>
+          <t>WukongAttack4</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>悟空挥棍4</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>WukongHurt</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>悟空受击语音</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>WukongDeath</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>悟空死亡语音</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>WukongImpact</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>悟空命中音(棍打中东西)</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>MenuTheme</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>开始与选角音乐</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>MapTheme</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>地图音乐</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>HuaguoshanTheme</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>花果山音乐</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>MenuConfirm</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>菜单确认音</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>Level.StageActivation</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>CameraArrived</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>相机抵达阶段右界</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32" s="0" t="inlineStr">
+        <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="I23" s="0" t="inlineStr">
+      <c r="I32" s="0" t="inlineStr">
         <is>
           <t>特殊区域激活</t>
         </is>
       </c>
-      <c r="J23" s="0" t="n">
+      <c r="J32" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>Stat.StatType</t>
         </is>
       </c>
-      <c r="C24" t="b">
+      <c r="C33" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D24" t="b">
+      <c r="D33" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H33" s="0" t="inlineStr">
         <is>
           <t>MaxHp</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I33" s="0" t="inlineStr">
         <is>
           <t>生命上限</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J33" s="0" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="H25" t="inlineStr">
+    <row r="34">
+      <c r="H34" s="0" t="inlineStr">
         <is>
           <t>MaxMp</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I34" s="0" t="inlineStr">
         <is>
           <t>魔法上限</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J34" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="26">
-      <c r="H26" t="inlineStr">
+    <row r="35">
+      <c r="H35" s="0" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I35" s="0" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J35" s="0" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="27">
-      <c r="H27" t="inlineStr">
+    <row r="36">
+      <c r="H36" s="0" t="inlineStr">
         <is>
           <t>Def</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I36" s="0" t="inlineStr">
         <is>
           <t>物防</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J36" s="0" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="28">
-      <c r="H28" t="inlineStr">
+    <row r="37">
+      <c r="H37" s="0" t="inlineStr">
         <is>
           <t>Mdef</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I37" s="0" t="inlineStr">
         <is>
           <t>魔防</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J37" s="0" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="29">
-      <c r="H29" t="inlineStr">
+    <row r="38">
+      <c r="H38" s="0" t="inlineStr">
         <is>
           <t>Crit</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I38" s="0" t="inlineStr">
         <is>
           <t>暴击</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J38" s="0" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="30">
-      <c r="H30" t="inlineStr">
+    <row r="39">
+      <c r="H39" s="0" t="inlineStr">
         <is>
           <t>Miss</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I39" s="0" t="inlineStr">
         <is>
           <t>闪避</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J39" s="0" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="31">
-      <c r="H31" t="inlineStr">
+    <row r="40">
+      <c r="H40" s="0" t="inlineStr">
         <is>
           <t>Lucky</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I40" s="0" t="inlineStr">
         <is>
           <t>幸运(加暴击倍率)</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J40" s="0" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="32">
-      <c r="H32" t="inlineStr">
+    <row r="41">
+      <c r="H41" s="0" t="inlineStr">
         <is>
           <t>Toughness</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I41" s="0" t="inlineStr">
         <is>
           <t>韧性(减对方幸运)</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J41" s="0" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="33">
-      <c r="H33" t="inlineStr">
+    <row r="42">
+      <c r="H42" s="0" t="inlineStr">
         <is>
           <t>Htarget</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I42" s="0" t="inlineStr">
         <is>
           <t>命中(减对方闪避)</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J42" s="0" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="34">
-      <c r="H34" t="inlineStr">
+    <row r="43">
+      <c r="H43" s="0" t="inlineStr">
         <is>
           <t>CritReduce</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I43" s="0" t="inlineStr">
         <is>
           <t>暴击抵抗</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J43" s="0" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="35">
-      <c r="H35" t="inlineStr">
+    <row r="44">
+      <c r="H44" s="0" t="inlineStr">
         <is>
           <t>Ar</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I44" s="0" t="inlineStr">
         <is>
           <t>破甲(减对方物防)</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="J44" s="0" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="36">
-      <c r="H36" t="inlineStr">
+    <row r="45">
+      <c r="H45" s="0" t="inlineStr">
         <is>
           <t>Sp</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I45" s="0" t="inlineStr">
         <is>
           <t>破魔(减对方魔防)</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J45" s="0" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="37">
-      <c r="H37" t="inlineStr">
+    <row r="46">
+      <c r="H46" s="0" t="inlineStr">
         <is>
           <t>Vampirism</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I46" s="0" t="inlineStr">
         <is>
           <t>吸血(百分点,伤害转生命)</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J46" s="0" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="38">
-      <c r="H38" t="inlineStr">
+    <row r="47">
+      <c r="H47" s="0" t="inlineStr">
         <is>
           <t>HpRegen</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I47" s="0" t="inlineStr">
         <is>
           <t>每秒回血</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J47" s="0" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="39">
-      <c r="H39" t="inlineStr">
+    <row r="48">
+      <c r="H48" s="0" t="inlineStr">
         <is>
           <t>MpRegen</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I48" s="0" t="inlineStr">
         <is>
           <t>每秒回蓝</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="J48" s="0" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>Stat.StatModifierKind</t>
         </is>
       </c>
-      <c r="C40" t="b">
+      <c r="C49" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D40" t="b">
+      <c r="D49" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H49" s="0" t="inlineStr">
         <is>
           <t>Flat</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I49" s="0" t="inlineStr">
         <is>
           <t>固定值</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="J49" s="0" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="H41" t="inlineStr">
+    <row r="50">
+      <c r="H50" s="0" t="inlineStr">
         <is>
           <t>PercentAdd</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I50" s="0" t="inlineStr">
         <is>
           <t>同类百分比相加</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="J50" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="42">
-      <c r="H42" t="inlineStr">
+    <row r="51">
+      <c r="H51" s="0" t="inlineStr">
         <is>
           <t>PercentMult</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I51" s="0" t="inlineStr">
         <is>
           <t>独立百分比相乘</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="J51" s="0" t="n">
         <v>2</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1361,6 +1361,9 @@
           <t>悟空</t>
         </is>
       </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="H12" s="0" t="inlineStr">
@@ -1373,6 +1376,9 @@
           <t>花果山猴子</t>
         </is>
       </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="H13" s="0" t="inlineStr">
@@ -1390,329 +1396,323 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="0" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>Gorilla</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>大猩猩</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>普通实体；由关卡指定为守关对手</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>Monster.MonsterRank</t>
         </is>
       </c>
-      <c r="C14" s="0" t="b">
+      <c r="C16" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D14" s="0" t="b">
+      <c r="D16" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="0" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I14" s="0" t="inlineStr">
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="J14" s="0" t="n">
+      <c r="J16" s="0" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="H15" s="0" t="inlineStr">
+    <row r="17">
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="I15" s="0" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t>精英</t>
         </is>
       </c>
-      <c r="J15" s="0" t="n">
+      <c r="J17" s="0" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="H16" s="0" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
-      <c r="I16" s="0" t="inlineStr">
-        <is>
-          <t>首领</t>
-        </is>
-      </c>
-      <c r="J16" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t>Battle.DamageKind</t>
-        </is>
-      </c>
-      <c r="C17" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" s="0" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="I17" s="0" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
       </c>
     </row>
     <row r="18">
       <c r="H18" s="0" t="inlineStr">
         <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>首领</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Battle.DamageKind</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" s="0" t="inlineStr">
+        <is>
           <t>Magic</t>
         </is>
       </c>
-      <c r="I18" s="0" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
         <is>
           <t>魔法</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="H19" s="0" t="inlineStr">
-        <is>
-          <t>Real</t>
-        </is>
-      </c>
-      <c r="I19" s="0" t="inlineStr">
-        <is>
-          <t>真实</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t>Sound.SoundId</t>
-        </is>
-      </c>
-      <c r="C20" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" s="0" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I20" s="0" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="J20" s="0" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t>WukongAttack2</t>
+          <t>Real</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>悟空挥棍2</t>
-        </is>
-      </c>
-      <c r="J21" s="0" t="n">
+          <t>真实</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="0" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22">
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>WukongAttack1And3</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t>悟空挥棍1/3</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J22" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t>WukongAttack4</t>
+          <t>WukongAttack2</t>
         </is>
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t>悟空挥棍4</t>
+          <t>悟空挥棍2</t>
         </is>
       </c>
       <c r="J23" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t>WukongHurt</t>
+          <t>WukongAttack1And3</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t>悟空受击语音</t>
+          <t>悟空挥棍1/3</t>
         </is>
       </c>
       <c r="J24" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="H25" s="0" t="inlineStr">
         <is>
-          <t>WukongDeath</t>
+          <t>WukongAttack4</t>
         </is>
       </c>
       <c r="I25" s="0" t="inlineStr">
         <is>
-          <t>悟空死亡语音</t>
+          <t>悟空挥棍4</t>
         </is>
       </c>
       <c r="J25" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t>WukongImpact</t>
+          <t>WukongHurt</t>
         </is>
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t>悟空命中音(棍打中东西)</t>
+          <t>悟空受击语音</t>
         </is>
       </c>
       <c r="J26" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>MenuTheme</t>
+          <t>WukongDeath</t>
         </is>
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t>开始与选角音乐</t>
+          <t>悟空死亡语音</t>
         </is>
       </c>
       <c r="J27" s="0" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>MapTheme</t>
+          <t>WukongImpact</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t>地图音乐</t>
+          <t>悟空命中音(棍打中东西)</t>
         </is>
       </c>
       <c r="J28" s="0" t="n">
-        <v>101</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>HuaguoshanTheme</t>
+          <t>MenuTheme</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t>花果山音乐</t>
+          <t>开始与选角音乐</t>
         </is>
       </c>
       <c r="J29" s="0" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>MenuConfirm</t>
+          <t>MapTheme</t>
         </is>
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t>菜单确认音</t>
+          <t>地图音乐</t>
         </is>
       </c>
       <c r="J30" s="0" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="0" t="inlineStr">
-        <is>
-          <t>Level.StageActivation</t>
-        </is>
-      </c>
-      <c r="C31" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>CameraArrived</t>
+          <t>HuaguoshanTheme</t>
         </is>
       </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>相机抵达阶段右界</t>
+          <t>花果山音乐</t>
         </is>
       </c>
       <c r="J31" s="0" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32">
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>MenuConfirm</t>
         </is>
       </c>
       <c r="I32" s="0" t="inlineStr">
         <is>
-          <t>特殊区域激活</t>
+          <t>菜单确认音</t>
         </is>
       </c>
       <c r="J32" s="0" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>Stat.StatType</t>
+          <t>Level.StageActivation</t>
         </is>
       </c>
       <c r="C33" s="0" t="b">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t>MaxHp</t>
+          <t>CameraArrived</t>
         </is>
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t>生命上限</t>
+          <t>相机抵达阶段右界</t>
         </is>
       </c>
       <c r="J33" s="0" t="n">
@@ -1738,12 +1738,12 @@
     <row r="34">
       <c r="H34" s="0" t="inlineStr">
         <is>
-          <t>MaxMp</t>
+          <t>Trigger</t>
         </is>
       </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
-          <t>魔法上限</t>
+          <t>特殊区域激活</t>
         </is>
       </c>
       <c r="J34" s="0" t="n">
@@ -1751,268 +1751,309 @@
       </c>
     </row>
     <row r="35">
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>Stat.StatType</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" s="0" t="b">
+        <v>1</v>
+      </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>MaxHp</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>生命上限</t>
         </is>
       </c>
       <c r="J35" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>Def</t>
+          <t>MaxMp</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t>物防</t>
+          <t>魔法上限</t>
         </is>
       </c>
       <c r="J36" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>Mdef</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t>魔防</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="J37" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>Crit</t>
+          <t>Def</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t>暴击</t>
+          <t>物防</t>
         </is>
       </c>
       <c r="J38" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Mdef</t>
         </is>
       </c>
       <c r="I39" s="0" t="inlineStr">
         <is>
-          <t>闪避</t>
+          <t>魔防</t>
         </is>
       </c>
       <c r="J39" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Crit</t>
         </is>
       </c>
       <c r="I40" s="0" t="inlineStr">
         <is>
-          <t>幸运(加暴击倍率)</t>
+          <t>暴击</t>
         </is>
       </c>
       <c r="J40" s="0" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="I41" s="0" t="inlineStr">
         <is>
-          <t>韧性(减对方幸运)</t>
+          <t>闪避</t>
         </is>
       </c>
       <c r="J41" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t>Htarget</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="I42" s="0" t="inlineStr">
         <is>
-          <t>命中(减对方闪避)</t>
+          <t>幸运(加暴击倍率)</t>
         </is>
       </c>
       <c r="J42" s="0" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>CritReduce</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="I43" s="0" t="inlineStr">
         <is>
-          <t>暴击抵抗</t>
+          <t>韧性(减对方幸运)</t>
         </is>
       </c>
       <c r="J43" s="0" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t>Ar</t>
+          <t>Htarget</t>
         </is>
       </c>
       <c r="I44" s="0" t="inlineStr">
         <is>
-          <t>破甲(减对方物防)</t>
+          <t>命中(减对方闪避)</t>
         </is>
       </c>
       <c r="J44" s="0" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="H45" s="0" t="inlineStr">
         <is>
-          <t>Sp</t>
+          <t>CritReduce</t>
         </is>
       </c>
       <c r="I45" s="0" t="inlineStr">
         <is>
-          <t>破魔(减对方魔防)</t>
+          <t>暴击抵抗</t>
         </is>
       </c>
       <c r="J45" s="0" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t>Vampirism</t>
+          <t>Ar</t>
         </is>
       </c>
       <c r="I46" s="0" t="inlineStr">
         <is>
-          <t>吸血(百分点,伤害转生命)</t>
+          <t>破甲(减对方物防)</t>
         </is>
       </c>
       <c r="J46" s="0" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47">
       <c r="H47" s="0" t="inlineStr">
         <is>
-          <t>HpRegen</t>
+          <t>Sp</t>
         </is>
       </c>
       <c r="I47" s="0" t="inlineStr">
         <is>
-          <t>每秒回血</t>
+          <t>破魔(减对方魔防)</t>
         </is>
       </c>
       <c r="J47" s="0" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48">
       <c r="H48" s="0" t="inlineStr">
         <is>
-          <t>MpRegen</t>
+          <t>Vampirism</t>
         </is>
       </c>
       <c r="I48" s="0" t="inlineStr">
         <is>
-          <t>每秒回蓝</t>
+          <t>吸血(百分点,伤害转生命)</t>
         </is>
       </c>
       <c r="J48" s="0" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="0" t="inlineStr">
-        <is>
-          <t>Stat.StatModifierKind</t>
-        </is>
-      </c>
-      <c r="C49" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D49" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H49" s="0" t="inlineStr">
         <is>
-          <t>Flat</t>
+          <t>HpRegen</t>
         </is>
       </c>
       <c r="I49" s="0" t="inlineStr">
         <is>
-          <t>固定值</t>
+          <t>每秒回血</t>
         </is>
       </c>
       <c r="J49" s="0" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50">
       <c r="H50" s="0" t="inlineStr">
         <is>
+          <t>MpRegen</t>
+        </is>
+      </c>
+      <c r="I50" s="0" t="inlineStr">
+        <is>
+          <t>每秒回蓝</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>Stat.StatModifierKind</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="0" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="I51" s="0" t="inlineStr">
+        <is>
+          <t>固定值</t>
+        </is>
+      </c>
+      <c r="J51" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="H52" s="0" t="inlineStr">
+        <is>
           <t>PercentAdd</t>
         </is>
       </c>
-      <c r="I50" s="0" t="inlineStr">
+      <c r="I52" s="0" t="inlineStr">
         <is>
           <t>同类百分比相加</t>
         </is>
       </c>
-      <c r="J50" s="0" t="n">
+      <c r="J52" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="51">
-      <c r="H51" s="0" t="inlineStr">
+    <row r="53">
+      <c r="H53" s="0" t="inlineStr">
         <is>
           <t>PercentMult</t>
         </is>
       </c>
-      <c r="I51" s="0" t="inlineStr">
+      <c r="I53" s="0" t="inlineStr">
         <is>
           <t>独立百分比相乘</t>
         </is>
       </c>
-      <c r="J51" s="0" t="n">
+      <c r="J53" s="0" t="n">
         <v>2</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1340,720 +1340,735 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="0" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SaveNoticeForm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>保存成功提示</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>Entity.EntityId</t>
         </is>
       </c>
-      <c r="C11" s="0" t="b">
+      <c r="C12" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D11" s="0" t="b">
+      <c r="D12" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H11" s="0" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>Wukong</t>
         </is>
       </c>
-      <c r="I11" s="0" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>悟空</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" s="0" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t>HuaguoshanMonkey</t>
-        </is>
-      </c>
-      <c r="I12" s="0" t="inlineStr">
-        <is>
-          <t>花果山猴子</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t>HuaguoshanMonkey</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t>妖猴</t>
+          <t>花果山猴子</t>
         </is>
       </c>
       <c r="J13" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="H14" s="0" t="inlineStr">
         <is>
+          <t>DemonMonkey</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>妖猴</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" s="0" t="inlineStr">
+        <is>
           <t>Gorilla</t>
         </is>
       </c>
-      <c r="I14" s="0" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>大猩猩</t>
         </is>
       </c>
-      <c r="J14" s="0" t="n">
+      <c r="J15" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K14" s="0" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t>普通实体；由关卡指定为守关对手</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="H15" t="inlineStr">
+    <row r="16">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="0" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>Monster.MonsterRank</t>
         </is>
       </c>
-      <c r="C16" s="0" t="b">
+      <c r="C17" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D16" s="0" t="b">
+      <c r="D17" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H16" s="0" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I16" s="0" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="J16" s="0" t="n">
+      <c r="J17" s="0" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="H17" s="0" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="I17" s="0" t="inlineStr">
-        <is>
-          <t>精英</t>
-        </is>
-      </c>
-      <c r="J17" s="0" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="H18" s="0" t="inlineStr">
         <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="H19" s="0" t="inlineStr">
+        <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="I18" s="0" t="inlineStr">
+      <c r="I19" s="0" t="inlineStr">
         <is>
           <t>首领</t>
         </is>
       </c>
-      <c r="J18" s="0" t="n">
+      <c r="J19" s="0" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="0" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>Battle.DamageKind</t>
         </is>
       </c>
-      <c r="C19" s="0" t="b">
+      <c r="C20" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D19" s="0" t="b">
+      <c r="D20" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H19" s="0" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="I19" s="0" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
         <is>
           <t>物理</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="H20" s="0" t="inlineStr">
-        <is>
-          <t>Magic</t>
-        </is>
-      </c>
-      <c r="I20" s="0" t="inlineStr">
-        <is>
-          <t>魔法</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="H21" s="0" t="inlineStr">
         <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>魔法</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="H22" s="0" t="inlineStr">
+        <is>
           <t>Real</t>
         </is>
       </c>
-      <c r="I21" s="0" t="inlineStr">
+      <c r="I22" s="0" t="inlineStr">
         <is>
           <t>真实</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="0" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>Sound.SoundId</t>
         </is>
       </c>
-      <c r="C22" s="0" t="b">
+      <c r="C23" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D22" s="0" t="b">
+      <c r="D23" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H22" s="0" t="inlineStr">
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I22" s="0" t="inlineStr">
+      <c r="I23" s="0" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J22" s="0" t="n">
+      <c r="J23" s="0" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="H23" s="0" t="inlineStr">
-        <is>
-          <t>WukongAttack2</t>
-        </is>
-      </c>
-      <c r="I23" s="0" t="inlineStr">
-        <is>
-          <t>悟空挥棍2</t>
-        </is>
-      </c>
-      <c r="J23" s="0" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t>WukongAttack1And3</t>
+          <t>WukongAttack2</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t>悟空挥棍1/3</t>
+          <t>悟空挥棍2</t>
         </is>
       </c>
       <c r="J24" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="H25" s="0" t="inlineStr">
         <is>
-          <t>WukongAttack4</t>
+          <t>WukongAttack1And3</t>
         </is>
       </c>
       <c r="I25" s="0" t="inlineStr">
         <is>
-          <t>悟空挥棍4</t>
+          <t>悟空挥棍1/3</t>
         </is>
       </c>
       <c r="J25" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t>WukongHurt</t>
+          <t>WukongAttack4</t>
         </is>
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t>悟空受击语音</t>
+          <t>悟空挥棍4</t>
         </is>
       </c>
       <c r="J26" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>WukongDeath</t>
+          <t>WukongHurt</t>
         </is>
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t>悟空死亡语音</t>
+          <t>悟空受击语音</t>
         </is>
       </c>
       <c r="J27" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>WukongImpact</t>
+          <t>WukongDeath</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t>悟空命中音(棍打中东西)</t>
+          <t>悟空死亡语音</t>
         </is>
       </c>
       <c r="J28" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>MenuTheme</t>
+          <t>WukongImpact</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t>开始与选角音乐</t>
+          <t>悟空命中音(棍打中东西)</t>
         </is>
       </c>
       <c r="J29" s="0" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>MapTheme</t>
+          <t>MenuTheme</t>
         </is>
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t>地图音乐</t>
+          <t>开始与选角音乐</t>
         </is>
       </c>
       <c r="J30" s="0" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>HuaguoshanTheme</t>
+          <t>MapTheme</t>
         </is>
       </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>花果山音乐</t>
+          <t>地图音乐</t>
         </is>
       </c>
       <c r="J31" s="0" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32">
       <c r="H32" s="0" t="inlineStr">
         <is>
+          <t>HuaguoshanTheme</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t>花果山音乐</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" s="0" t="inlineStr">
+        <is>
           <t>MenuConfirm</t>
         </is>
       </c>
-      <c r="I32" s="0" t="inlineStr">
+      <c r="I33" s="0" t="inlineStr">
         <is>
           <t>菜单确认音</t>
         </is>
       </c>
-      <c r="J32" s="0" t="n">
+      <c r="J33" s="0" t="n">
         <v>103</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="0" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>Level.StageActivation</t>
         </is>
       </c>
-      <c r="C33" s="0" t="b">
+      <c r="C34" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D33" s="0" t="b">
+      <c r="D34" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H33" s="0" t="inlineStr">
+      <c r="H34" s="0" t="inlineStr">
         <is>
           <t>CameraArrived</t>
         </is>
       </c>
-      <c r="I33" s="0" t="inlineStr">
+      <c r="I34" s="0" t="inlineStr">
         <is>
           <t>相机抵达阶段右界</t>
         </is>
       </c>
-      <c r="J33" s="0" t="n">
+      <c r="J34" s="0" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="34">
-      <c r="H34" s="0" t="inlineStr">
+    <row r="35">
+      <c r="H35" s="0" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="I34" s="0" t="inlineStr">
+      <c r="I35" s="0" t="inlineStr">
         <is>
           <t>特殊区域激活</t>
         </is>
       </c>
-      <c r="J34" s="0" t="n">
+      <c r="J35" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="0" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>Stat.StatType</t>
         </is>
       </c>
-      <c r="C35" s="0" t="b">
+      <c r="C36" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D35" s="0" t="b">
+      <c r="D36" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H35" s="0" t="inlineStr">
+      <c r="H36" s="0" t="inlineStr">
         <is>
           <t>MaxHp</t>
         </is>
       </c>
-      <c r="I35" s="0" t="inlineStr">
+      <c r="I36" s="0" t="inlineStr">
         <is>
           <t>生命上限</t>
         </is>
       </c>
-      <c r="J35" s="0" t="n">
+      <c r="J36" s="0" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="H36" s="0" t="inlineStr">
-        <is>
-          <t>MaxMp</t>
-        </is>
-      </c>
-      <c r="I36" s="0" t="inlineStr">
-        <is>
-          <t>魔法上限</t>
-        </is>
-      </c>
-      <c r="J36" s="0" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>MaxMp</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>魔法上限</t>
         </is>
       </c>
       <c r="J37" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>Def</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t>物防</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="J38" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t>Mdef</t>
+          <t>Def</t>
         </is>
       </c>
       <c r="I39" s="0" t="inlineStr">
         <is>
-          <t>魔防</t>
+          <t>物防</t>
         </is>
       </c>
       <c r="J39" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>Crit</t>
+          <t>Mdef</t>
         </is>
       </c>
       <c r="I40" s="0" t="inlineStr">
         <is>
-          <t>暴击</t>
+          <t>魔防</t>
         </is>
       </c>
       <c r="J40" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Crit</t>
         </is>
       </c>
       <c r="I41" s="0" t="inlineStr">
         <is>
-          <t>闪避</t>
+          <t>暴击</t>
         </is>
       </c>
       <c r="J41" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="I42" s="0" t="inlineStr">
         <is>
-          <t>幸运(加暴击倍率)</t>
+          <t>闪避</t>
         </is>
       </c>
       <c r="J42" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="I43" s="0" t="inlineStr">
         <is>
-          <t>韧性(减对方幸运)</t>
+          <t>幸运(加暴击倍率)</t>
         </is>
       </c>
       <c r="J43" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t>Htarget</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="I44" s="0" t="inlineStr">
         <is>
-          <t>命中(减对方闪避)</t>
+          <t>韧性(减对方幸运)</t>
         </is>
       </c>
       <c r="J44" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="H45" s="0" t="inlineStr">
         <is>
-          <t>CritReduce</t>
+          <t>Htarget</t>
         </is>
       </c>
       <c r="I45" s="0" t="inlineStr">
         <is>
-          <t>暴击抵抗</t>
+          <t>命中(减对方闪避)</t>
         </is>
       </c>
       <c r="J45" s="0" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t>Ar</t>
+          <t>CritReduce</t>
         </is>
       </c>
       <c r="I46" s="0" t="inlineStr">
         <is>
-          <t>破甲(减对方物防)</t>
+          <t>暴击抵抗</t>
         </is>
       </c>
       <c r="J46" s="0" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
       <c r="H47" s="0" t="inlineStr">
         <is>
-          <t>Sp</t>
+          <t>Ar</t>
         </is>
       </c>
       <c r="I47" s="0" t="inlineStr">
         <is>
-          <t>破魔(减对方魔防)</t>
+          <t>破甲(减对方物防)</t>
         </is>
       </c>
       <c r="J47" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="H48" s="0" t="inlineStr">
         <is>
-          <t>Vampirism</t>
+          <t>Sp</t>
         </is>
       </c>
       <c r="I48" s="0" t="inlineStr">
         <is>
-          <t>吸血(百分点,伤害转生命)</t>
+          <t>破魔(减对方魔防)</t>
         </is>
       </c>
       <c r="J48" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49">
       <c r="H49" s="0" t="inlineStr">
         <is>
-          <t>HpRegen</t>
+          <t>Vampirism</t>
         </is>
       </c>
       <c r="I49" s="0" t="inlineStr">
         <is>
-          <t>每秒回血</t>
+          <t>吸血(百分点,伤害转生命)</t>
         </is>
       </c>
       <c r="J49" s="0" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50">
       <c r="H50" s="0" t="inlineStr">
         <is>
+          <t>HpRegen</t>
+        </is>
+      </c>
+      <c r="I50" s="0" t="inlineStr">
+        <is>
+          <t>每秒回血</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="H51" s="0" t="inlineStr">
+        <is>
           <t>MpRegen</t>
         </is>
       </c>
-      <c r="I50" s="0" t="inlineStr">
+      <c r="I51" s="0" t="inlineStr">
         <is>
           <t>每秒回蓝</t>
         </is>
       </c>
-      <c r="J50" s="0" t="n">
+      <c r="J51" s="0" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="0" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>Stat.StatModifierKind</t>
         </is>
       </c>
-      <c r="C51" s="0" t="b">
+      <c r="C52" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D51" s="0" t="b">
+      <c r="D52" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="H51" s="0" t="inlineStr">
+      <c r="H52" s="0" t="inlineStr">
         <is>
           <t>Flat</t>
         </is>
       </c>
-      <c r="I51" s="0" t="inlineStr">
+      <c r="I52" s="0" t="inlineStr">
         <is>
           <t>固定值</t>
         </is>
       </c>
-      <c r="J51" s="0" t="n">
+      <c r="J52" s="0" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="H52" s="0" t="inlineStr">
-        <is>
-          <t>PercentAdd</t>
-        </is>
-      </c>
-      <c r="I52" s="0" t="inlineStr">
-        <is>
-          <t>同类百分比相加</t>
-        </is>
-      </c>
-      <c r="J52" s="0" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="H53" s="0" t="inlineStr">
         <is>
+          <t>PercentAdd</t>
+        </is>
+      </c>
+      <c r="I53" s="0" t="inlineStr">
+        <is>
+          <t>同类百分比相加</t>
+        </is>
+      </c>
+      <c r="J53" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="H54" s="0" t="inlineStr">
+        <is>
           <t>PercentMult</t>
         </is>
       </c>
-      <c r="I53" s="0" t="inlineStr">
+      <c r="I54" s="0" t="inlineStr">
         <is>
           <t>独立百分比相乘</t>
         </is>
       </c>
-      <c r="J53" s="0" t="n">
+      <c r="J54" s="0" t="n">
         <v>2</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R851bcf368e8145f8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R51eb06ec8bf3476e"/>
   </sheets>
 </workbook>
 </file>
@@ -624,7 +624,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -639,6 +639,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+      <extLst>
+        <ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -761,6 +769,23 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1332,56 +1357,52 @@
     </row>
     <row r="14">
       <c r="A14"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Entity.EntityId</t>
-        </is>
-      </c>
-      <c r="C14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wukong</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">悟空</t>
-        </is>
+      <c r="H14" t="str">
+        <v>SkillForm</v>
+      </c>
+      <c r="I14" t="str">
+        <v>造一技能面板</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14"/>
     </row>
     <row r="15">
       <c r="A15"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entity.EntityId</t>
+        </is>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HuaguoshanMonkey</t>
+          <t xml:space="preserve">Wukong</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">花果山猴子</t>
+          <t xml:space="preserve">悟空</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15"/>
@@ -1396,16 +1417,16 @@
       <c r="G16" s="1"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DemonMonkey</t>
+          <t xml:space="preserve">HuaguoshanMonkey</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">妖猴</t>
+          <t xml:space="preserve">花果山猴子</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16"/>
@@ -1420,22 +1441,18 @@
       <c r="G17" s="1"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gorilla</t>
+          <t xml:space="preserve">DemonMonkey</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">大猩猩</t>
+          <t xml:space="preserve">妖猴</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">普通实体；由关卡指定为守关对手</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K17" s="1"/>
       <c r="L17"/>
     </row>
     <row r="18">
@@ -1448,72 +1465,76 @@
       <c r="G18" s="1"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">Gorilla</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">无</t>
+          <t xml:space="preserve">大猩猩</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K18" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">普通实体；由关卡指定为守关对手</t>
+        </is>
+      </c>
       <c r="L18"/>
     </row>
     <row r="19">
       <c r="A19"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Monster.MonsterRank</t>
-        </is>
-      </c>
-      <c r="C19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normal</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">普通</t>
+          <t xml:space="preserve">无</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19"/>
     </row>
     <row r="20">
       <c r="A20"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monster.MonsterRank</t>
+        </is>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elite</t>
+          <t xml:space="preserve">Normal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">精英</t>
+          <t xml:space="preserve">普通</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20"/>
@@ -1528,66 +1549,68 @@
       <c r="G21" s="1"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boss</t>
+          <t xml:space="preserve">Elite</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">首领</t>
+          <t xml:space="preserve">精英</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21"/>
     </row>
     <row r="22">
       <c r="A22"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Battle.DamageKind</t>
-        </is>
-      </c>
-      <c r="C22" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physics</t>
+          <t xml:space="preserve">Boss</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理</t>
-        </is>
-      </c>
-      <c r="J22" s="1"/>
+          <t xml:space="preserve">首领</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
       <c r="K22" s="1"/>
       <c r="L22"/>
     </row>
     <row r="23">
       <c r="A23"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Battle.DamageKind</t>
+        </is>
+      </c>
+      <c r="C23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magic</t>
+          <t xml:space="preserve">Physics</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔法</t>
+          <t xml:space="preserve">物理</t>
         </is>
       </c>
       <c r="J23" s="1"/>
@@ -1604,12 +1627,12 @@
       <c r="G24" s="1"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real</t>
+          <t xml:space="preserve">Magic</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">真实</t>
+          <t xml:space="preserve">魔法</t>
         </is>
       </c>
       <c r="J24" s="1"/>
@@ -1618,52 +1641,54 @@
     </row>
     <row r="25">
       <c r="A25"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sound.SoundId</t>
-        </is>
-      </c>
-      <c r="C25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">Real</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">无</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
+          <t xml:space="preserve">真实</t>
+        </is>
+      </c>
+      <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25"/>
     </row>
     <row r="26">
       <c r="A26"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="C26" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" t="str">
-        <v>WukongAttack1And2</v>
-      </c>
-      <c r="I26" t="str">
-        <v>悟空挥棍1/2</v>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无</t>
+        </is>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26"/>
@@ -1677,13 +1702,13 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" t="str">
-        <v>WukongAttack3And4</v>
+        <v>WukongAttack1And2</v>
       </c>
       <c r="I27" t="str">
-        <v>悟空挥棍3/4</v>
+        <v>悟空挥棍1/2</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27"/>
@@ -1697,13 +1722,13 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" t="str">
-        <v>WukongAttack5</v>
+        <v>WukongAttack3And4</v>
       </c>
       <c r="I28" t="str">
-        <v>悟空挥棍5</v>
+        <v>悟空挥棍3/4</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28"/>
@@ -1716,18 +1741,14 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WukongHurt</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">悟空受击语音</t>
-        </is>
+      <c r="H29" t="str">
+        <v>WukongAttack5</v>
+      </c>
+      <c r="I29" t="str">
+        <v>悟空挥棍5</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29"/>
@@ -1742,16 +1763,16 @@
       <c r="G30" s="1"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WukongDeath</t>
+          <t xml:space="preserve">WukongHurt</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">悟空死亡语音</t>
+          <t xml:space="preserve">悟空受击语音</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30"/>
@@ -1766,16 +1787,16 @@
       <c r="G31" s="1"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">WukongImpact</t>
+          <t xml:space="preserve">WukongDeath</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">悟空命中音(棍打中东西)</t>
+          <t xml:space="preserve">悟空死亡语音</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31"/>
@@ -1790,16 +1811,16 @@
       <c r="G32" s="1"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">MenuTheme</t>
+          <t xml:space="preserve">WukongImpact</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">开始与选角音乐</t>
+          <t xml:space="preserve">悟空命中音(棍打中东西)</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32"/>
@@ -1814,16 +1835,16 @@
       <c r="G33" s="1"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">MapTheme</t>
+          <t xml:space="preserve">MenuTheme</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图音乐</t>
+          <t xml:space="preserve">开始与选角音乐</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33"/>
@@ -1838,16 +1859,16 @@
       <c r="G34" s="1"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">HuaguoshanTheme</t>
+          <t xml:space="preserve">MapTheme</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">花果山音乐</t>
+          <t xml:space="preserve">地图音乐</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34"/>
@@ -1862,48 +1883,40 @@
       <c r="G35" s="1"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MenuConfirm</t>
+          <t xml:space="preserve">HuaguoshanTheme</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">菜单确认音</t>
+          <t xml:space="preserve">花果山音乐</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35"/>
     </row>
     <row r="36">
       <c r="A36"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Level.StageActivation</t>
-        </is>
-      </c>
-      <c r="C36" t="b">
-        <v>0</v>
-      </c>
-      <c r="D36" t="b">
-        <v>1</v>
-      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">CameraArrived</t>
+          <t xml:space="preserve">MenuConfirm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">相机抵达阶段右界</t>
+          <t xml:space="preserve">菜单确认音</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36"/>
@@ -1916,48 +1929,34 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trigger</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">特殊区域激活</t>
-        </is>
+      <c r="H37" t="str">
+        <v>WukongRisingDragon</v>
+      </c>
+      <c r="I37" t="str">
+        <v>悟空升龙斩</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37"/>
     </row>
     <row r="38">
       <c r="A38"/>
-      <c r="B38" t="str">
-        <v>Attributes.AttributeType</v>
-      </c>
-      <c r="C38" t="b">
-        <v>0</v>
-      </c>
-      <c r="D38" t="b">
-        <v>1</v>
-      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MaxHp</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">生命上限</t>
-        </is>
+      <c r="H38" t="str">
+        <v>WukongFlameThrust</v>
+      </c>
+      <c r="I38" t="str">
+        <v>悟空火炎突击</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38"/>
@@ -1970,18 +1969,14 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MaxMp</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">魔法上限</t>
-        </is>
+      <c r="H39" t="str">
+        <v>WukongBlazingFlash</v>
+      </c>
+      <c r="I39" t="str">
+        <v>悟空烈焰闪</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K39" s="1"/>
       <c r="L39"/>
@@ -1994,18 +1989,14 @@
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Power</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">攻击</t>
-        </is>
+      <c r="H40" t="str">
+        <v>WukongFlameStorm</v>
+      </c>
+      <c r="I40" t="str">
+        <v>悟空烈焰风暴</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K40" s="1"/>
       <c r="L40"/>
@@ -2018,18 +2009,14 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Def</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">物防</t>
-        </is>
+      <c r="H41" t="str">
+        <v>WukongFireDemonStart</v>
+      </c>
+      <c r="I41" t="str">
+        <v>悟空火魔斩起手</v>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41"/>
@@ -2042,18 +2029,14 @@
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mdef</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">魔防</t>
-        </is>
+      <c r="H42" t="str">
+        <v>WukongFireDemonCombo</v>
+      </c>
+      <c r="I42" t="str">
+        <v>悟空火魔九连斩</v>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K42" s="1"/>
       <c r="L42"/>
@@ -2066,42 +2049,46 @@
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crit</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">暴击</t>
-        </is>
+      <c r="H43" t="str">
+        <v>WukongFireDemonLanding</v>
+      </c>
+      <c r="I43" t="str">
+        <v>悟空火魔斩落地</v>
       </c>
       <c r="J43" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43"/>
     </row>
     <row r="44">
       <c r="A44"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Level.StageActivation</t>
+        </is>
+      </c>
+      <c r="C44" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miss</t>
+          <t xml:space="preserve">CameraArrived</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">闪避</t>
+          <t xml:space="preserve">相机抵达阶段右界</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44"/>
@@ -2116,40 +2103,46 @@
       <c r="G45" s="1"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucky</t>
+          <t xml:space="preserve">Trigger</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">幸运(加暴击倍率)</t>
+          <t xml:space="preserve">特殊区域激活</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45"/>
     </row>
     <row r="46">
       <c r="A46"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
+      <c r="B46" t="str">
+        <v>Attributes.AttributeType</v>
+      </c>
+      <c r="C46" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" t="b">
+        <v>1</v>
+      </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
+          <t xml:space="preserve">MaxHp</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">韧性(减对方幸运)</t>
+          <t xml:space="preserve">生命上限</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46"/>
@@ -2164,16 +2157,16 @@
       <c r="G47" s="1"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Htarget</t>
+          <t xml:space="preserve">MaxMp</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">命中(减对方闪避)</t>
+          <t xml:space="preserve">魔法上限</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47"/>
@@ -2188,16 +2181,16 @@
       <c r="G48" s="1"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">CritReduce</t>
+          <t xml:space="preserve">Power</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴击抵抗</t>
+          <t xml:space="preserve">攻击</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48"/>
@@ -2212,16 +2205,16 @@
       <c r="G49" s="1"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ar</t>
+          <t xml:space="preserve">Def</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">破甲(减对方物防)</t>
+          <t xml:space="preserve">物防</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49"/>
@@ -2236,16 +2229,16 @@
       <c r="G50" s="1"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sp</t>
+          <t xml:space="preserve">Mdef</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">破魔(减对方魔防)</t>
+          <t xml:space="preserve">魔防</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K50" s="1"/>
       <c r="L50"/>
@@ -2260,16 +2253,16 @@
       <c r="G51" s="1"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vampirism</t>
+          <t xml:space="preserve">Crit</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">吸血(百分点,伤害转生命)</t>
+          <t xml:space="preserve">暴击</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51"/>
@@ -2284,16 +2277,16 @@
       <c r="G52" s="1"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">HpRegen</t>
+          <t xml:space="preserve">Miss</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">每秒回血</t>
+          <t xml:space="preserve">闪避</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K52" s="1"/>
       <c r="L52"/>
@@ -2308,46 +2301,40 @@
       <c r="G53" s="1"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">MpRegen</t>
+          <t xml:space="preserve">Lucky</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">每秒回蓝</t>
+          <t xml:space="preserve">幸运(加暴击倍率)</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53"/>
     </row>
     <row r="54">
       <c r="A54"/>
-      <c r="B54" t="str">
-        <v>Attributes.AttributeModifierKind</v>
-      </c>
-      <c r="C54" t="b">
-        <v>0</v>
-      </c>
-      <c r="D54" t="b">
-        <v>1</v>
-      </c>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flat</t>
+          <t xml:space="preserve">Toughness</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">固定值</t>
+          <t xml:space="preserve">韧性(减对方幸运)</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54"/>
@@ -2362,16 +2349,16 @@
       <c r="G55" s="1"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">PercentAdd</t>
+          <t xml:space="preserve">Htarget</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">同类百分比相加</t>
+          <t xml:space="preserve">命中(减对方闪避)</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55"/>
@@ -2386,225 +2373,257 @@
       <c r="G56" s="1"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">PercentMult</t>
+          <t xml:space="preserve">CritReduce</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">独立百分比相乘</t>
+          <t xml:space="preserve">暴击抵抗</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K56" s="1"/>
       <c r="L56"/>
     </row>
     <row r="57">
       <c r="A57"/>
-      <c r="B57" t="str">
-        <v>Equipment.EquipmentId</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57"/>
-      <c r="F57"/>
-      <c r="G57"/>
-      <c r="H57" t="str">
-        <v>None</v>
-      </c>
-      <c r="I57" t="str">
-        <v>无装备</v>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ar</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破甲(减对方物防)</t>
+        </is>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57"/>
+        <v>11</v>
+      </c>
+      <c r="K57" s="1"/>
       <c r="L57"/>
     </row>
     <row r="58">
       <c r="A58"/>
-      <c r="B58"/>
-      <c r="C58"/>
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58"/>
-      <c r="G58"/>
-      <c r="H58" t="str">
-        <v>RoughPilgrimClothes</v>
-      </c>
-      <c r="I58" t="str">
-        <v>粗糙的行者服</v>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sp</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破魔(减对方魔防)</t>
+        </is>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58"/>
+        <v>12</v>
+      </c>
+      <c r="K58" s="1"/>
       <c r="L58"/>
     </row>
     <row r="59">
       <c r="A59"/>
-      <c r="B59"/>
-      <c r="C59"/>
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59"/>
-      <c r="G59"/>
-      <c r="H59" t="str">
-        <v>RoughPilgrimStaff</v>
-      </c>
-      <c r="I59" t="str">
-        <v>粗糙的行者棍</v>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vampirism</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吸血(百分点,伤害转生命)</t>
+        </is>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
-      </c>
-      <c r="K59"/>
+        <v>13</v>
+      </c>
+      <c r="K59" s="1"/>
       <c r="L59"/>
     </row>
     <row r="60">
       <c r="A60"/>
-      <c r="B60"/>
-      <c r="C60"/>
-      <c r="D60"/>
-      <c r="E60"/>
-      <c r="F60"/>
-      <c r="G60"/>
-      <c r="H60" t="str">
-        <v>RoughCassock</v>
-      </c>
-      <c r="I60" t="str">
-        <v>粗糙的袈裟</v>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HpRegen</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每秒回血</t>
+        </is>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
-      </c>
-      <c r="K60"/>
+        <v>14</v>
+      </c>
+      <c r="K60" s="1"/>
       <c r="L60"/>
     </row>
     <row r="61">
       <c r="A61"/>
-      <c r="B61"/>
-      <c r="C61"/>
-      <c r="D61"/>
-      <c r="E61"/>
-      <c r="F61"/>
-      <c r="G61"/>
-      <c r="H61" t="str">
-        <v>RoughPineStaff</v>
-      </c>
-      <c r="I61" t="str">
-        <v>粗糙的松木杖</v>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MpRegen</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每秒回蓝</t>
+        </is>
       </c>
       <c r="J61" t="n">
-        <v>4</v>
-      </c>
-      <c r="K61"/>
+        <v>15</v>
+      </c>
+      <c r="K61" s="1"/>
       <c r="L61"/>
     </row>
     <row r="62">
       <c r="A62"/>
-      <c r="B62"/>
-      <c r="C62"/>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
-      <c r="G62"/>
-      <c r="H62" t="str">
-        <v>CommonPilgrimClothes</v>
-      </c>
-      <c r="I62" t="str">
-        <v>普通的行者服</v>
+      <c r="B62" t="str">
+        <v>Attributes.AttributeModifierKind</v>
+      </c>
+      <c r="C62" t="b">
+        <v>0</v>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">固定值</t>
+        </is>
       </c>
       <c r="J62" t="n">
-        <v>5</v>
-      </c>
-      <c r="K62"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="1"/>
       <c r="L62"/>
     </row>
     <row r="63">
       <c r="A63"/>
-      <c r="B63"/>
-      <c r="C63"/>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
-      <c r="G63"/>
-      <c r="H63" t="str">
-        <v>CommonPilgrimStaff</v>
-      </c>
-      <c r="I63" t="str">
-        <v>普通的行者棍</v>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PercentAdd</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同类百分比相加</t>
+        </is>
       </c>
       <c r="J63" t="n">
-        <v>6</v>
-      </c>
-      <c r="K63"/>
+        <v>1</v>
+      </c>
+      <c r="K63" s="1"/>
       <c r="L63"/>
     </row>
     <row r="64">
       <c r="A64"/>
-      <c r="B64"/>
-      <c r="C64"/>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
-      <c r="G64"/>
-      <c r="H64" t="str">
-        <v>CommonCassock</v>
-      </c>
-      <c r="I64" t="str">
-        <v>普通的袈裟</v>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PercentMult</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">独立百分比相乘</t>
+        </is>
       </c>
       <c r="J64" t="n">
-        <v>7</v>
-      </c>
-      <c r="K64"/>
+        <v>2</v>
+      </c>
+      <c r="K64" s="1"/>
       <c r="L64"/>
     </row>
     <row r="65">
       <c r="A65"/>
-      <c r="B65"/>
-      <c r="C65"/>
-      <c r="D65"/>
+      <c r="B65" t="str">
+        <v>Equipment.EquipmentId</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
       <c r="E65"/>
       <c r="F65"/>
       <c r="G65"/>
       <c r="H65" t="str">
-        <v>CommonPineStaff</v>
+        <v>None</v>
       </c>
       <c r="I65" t="str">
-        <v>普通的松木杖</v>
+        <v>无装备</v>
       </c>
       <c r="J65" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K65"/>
       <c r="L65"/>
     </row>
     <row r="66">
       <c r="A66"/>
-      <c r="B66" t="str">
-        <v>Equipment.EquipmentOwner</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1</v>
-      </c>
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66"/>
       <c r="E66"/>
       <c r="F66"/>
       <c r="G66"/>
       <c r="H66" t="str">
-        <v>Wukong</v>
+        <v>RoughPilgrimClothes</v>
       </c>
       <c r="I66" t="str">
-        <v>悟空</v>
+        <v>粗糙的行者服</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
@@ -2621,10 +2640,10 @@
       <c r="F67"/>
       <c r="G67"/>
       <c r="H67" t="str">
-        <v>Tangseng</v>
+        <v>RoughPilgrimStaff</v>
       </c>
       <c r="I67" t="str">
-        <v>唐僧</v>
+        <v>粗糙的行者棍</v>
       </c>
       <c r="J67" t="n">
         <v>2</v>
@@ -2634,26 +2653,20 @@
     </row>
     <row r="68">
       <c r="A68"/>
-      <c r="B68" t="str">
-        <v>Equipment.EquipmentSlot</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1</v>
-      </c>
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="D68"/>
       <c r="E68"/>
       <c r="F68"/>
       <c r="G68"/>
       <c r="H68" t="str">
-        <v>Weapon</v>
+        <v>RoughCassock</v>
       </c>
       <c r="I68" t="str">
-        <v>武器</v>
+        <v>粗糙的袈裟</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K68"/>
       <c r="L68"/>
@@ -2667,39 +2680,33 @@
       <c r="F69"/>
       <c r="G69"/>
       <c r="H69" t="str">
-        <v>Armor</v>
+        <v>RoughPineStaff</v>
       </c>
       <c r="I69" t="str">
-        <v>防具</v>
+        <v>粗糙的松木杖</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K69"/>
       <c r="L69"/>
     </row>
     <row r="70">
       <c r="A70"/>
-      <c r="B70" t="str">
-        <v>Equipment.EquipmentQuality</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1</v>
-      </c>
+      <c r="B70"/>
+      <c r="C70"/>
+      <c r="D70"/>
       <c r="E70"/>
       <c r="F70"/>
       <c r="G70"/>
       <c r="H70" t="str">
-        <v>Rough</v>
+        <v>CommonPilgrimClothes</v>
       </c>
       <c r="I70" t="str">
-        <v>粗糙</v>
+        <v>普通的行者服</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K70"/>
       <c r="L70"/>
@@ -2713,13 +2720,13 @@
       <c r="F71"/>
       <c r="G71"/>
       <c r="H71" t="str">
-        <v>Common</v>
+        <v>CommonPilgrimStaff</v>
       </c>
       <c r="I71" t="str">
-        <v>普通</v>
+        <v>普通的行者棍</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K71"/>
       <c r="L71"/>
@@ -2733,13 +2740,13 @@
       <c r="F72"/>
       <c r="G72"/>
       <c r="H72" t="str">
-        <v>Excellent</v>
+        <v>CommonCassock</v>
       </c>
       <c r="I72" t="str">
-        <v>优秀</v>
+        <v>普通的袈裟</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K72"/>
       <c r="L72"/>
@@ -2753,33 +2760,39 @@
       <c r="F73"/>
       <c r="G73"/>
       <c r="H73" t="str">
-        <v>Fine</v>
+        <v>CommonPineStaff</v>
       </c>
       <c r="I73" t="str">
-        <v>精良</v>
+        <v>普通的松木杖</v>
       </c>
       <c r="J73" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K73"/>
       <c r="L73"/>
     </row>
     <row r="74">
       <c r="A74"/>
-      <c r="B74"/>
-      <c r="C74"/>
-      <c r="D74"/>
+      <c r="B74" t="str">
+        <v>Equipment.EquipmentOwner</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
       <c r="E74"/>
       <c r="F74"/>
       <c r="G74"/>
       <c r="H74" t="str">
-        <v>Epic</v>
+        <v>Wukong</v>
       </c>
       <c r="I74" t="str">
-        <v>史诗</v>
+        <v>悟空</v>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K74"/>
       <c r="L74"/>
@@ -2793,13 +2806,13 @@
       <c r="F75"/>
       <c r="G75"/>
       <c r="H75" t="str">
-        <v>Legendary</v>
+        <v>Tangseng</v>
       </c>
       <c r="I75" t="str">
-        <v>传说</v>
+        <v>唐僧</v>
       </c>
       <c r="J75" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K75"/>
       <c r="L75"/>
@@ -2807,7 +2820,7 @@
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="str">
-        <v>Loot.EquipmentDropPoolId</v>
+        <v>Equipment.EquipmentSlot</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -2819,13 +2832,13 @@
       <c r="F76"/>
       <c r="G76"/>
       <c r="H76" t="str">
-        <v>UseMonster</v>
+        <v>Weapon</v>
       </c>
       <c r="I76" t="str">
-        <v>继承怪物</v>
+        <v>武器</v>
       </c>
       <c r="J76" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K76"/>
       <c r="L76"/>
@@ -2839,22 +2852,28 @@
       <c r="F77"/>
       <c r="G77"/>
       <c r="H77" t="str">
-        <v>None</v>
+        <v>Armor</v>
       </c>
       <c r="I77" t="str">
-        <v>不掉落</v>
+        <v>防具</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77"/>
       <c r="L77"/>
     </row>
     <row r="78">
       <c r="A78"/>
-      <c r="B78"/>
-      <c r="C78"/>
-      <c r="D78"/>
+      <c r="B78" t="str">
+        <v>Equipment.EquipmentQuality</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
       <c r="E78"/>
       <c r="F78"/>
       <c r="G78"/>
@@ -2862,10 +2881,10 @@
         <v>Rough</v>
       </c>
       <c r="I78" t="str">
-        <v>粗糙装备</v>
+        <v>粗糙</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78"/>
       <c r="L78"/>
@@ -2882,34 +2901,30 @@
         <v>Common</v>
       </c>
       <c r="I79" t="str">
-        <v>普通装备</v>
+        <v>普通</v>
       </c>
       <c r="J79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K79"/>
       <c r="L79"/>
     </row>
     <row r="80">
       <c r="A80"/>
-      <c r="B80" t="str">
-        <v>Loot.PickupId</v>
-      </c>
-      <c r="C80" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1</v>
-      </c>
+      <c r="B80"/>
+      <c r="C80"/>
+      <c r="D80"/>
       <c r="E80"/>
       <c r="F80"/>
       <c r="G80"/>
       <c r="H80" t="str">
-        <v>None</v>
-      </c>
-      <c r="I80"/>
+        <v>Excellent</v>
+      </c>
+      <c r="I80" t="str">
+        <v>优秀</v>
+      </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K80"/>
       <c r="L80"/>
@@ -2923,11 +2938,13 @@
       <c r="F81"/>
       <c r="G81"/>
       <c r="H81" t="str">
-        <v>SmallPeach</v>
-      </c>
-      <c r="I81"/>
+        <v>Fine</v>
+      </c>
+      <c r="I81" t="str">
+        <v>精良</v>
+      </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K81"/>
       <c r="L81"/>
@@ -2941,11 +2958,13 @@
       <c r="F82"/>
       <c r="G82"/>
       <c r="H82" t="str">
-        <v>LargePeach</v>
-      </c>
-      <c r="I82"/>
+        <v>Epic</v>
+      </c>
+      <c r="I82" t="str">
+        <v>史诗</v>
+      </c>
       <c r="J82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K82"/>
       <c r="L82"/>
@@ -2959,11 +2978,13 @@
       <c r="F83"/>
       <c r="G83"/>
       <c r="H83" t="str">
-        <v>ManaBottle</v>
-      </c>
-      <c r="I83"/>
+        <v>Legendary</v>
+      </c>
+      <c r="I83" t="str">
+        <v>传说</v>
+      </c>
       <c r="J83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K83"/>
       <c r="L83"/>
@@ -2971,7 +2992,7 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="str">
-        <v>Loot.PickupEffect</v>
+        <v>Loot.EquipmentDropPoolId</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -2983,11 +3004,13 @@
       <c r="F84"/>
       <c r="G84"/>
       <c r="H84" t="str">
-        <v>Health</v>
-      </c>
-      <c r="I84"/>
+        <v>UseMonster</v>
+      </c>
+      <c r="I84" t="str">
+        <v>继承怪物</v>
+      </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K84"/>
       <c r="L84"/>
@@ -3001,14 +3024,1642 @@
       <c r="F85"/>
       <c r="G85"/>
       <c r="H85" t="str">
-        <v>Mana</v>
-      </c>
-      <c r="I85"/>
+        <v>None</v>
+      </c>
+      <c r="I85" t="str">
+        <v>不掉落</v>
+      </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85"/>
       <c r="L85"/>
+    </row>
+    <row r="86">
+      <c r="A86"/>
+      <c r="B86"/>
+      <c r="C86"/>
+      <c r="D86"/>
+      <c r="E86"/>
+      <c r="F86"/>
+      <c r="G86"/>
+      <c r="H86" t="str">
+        <v>Rough</v>
+      </c>
+      <c r="I86" t="str">
+        <v>粗糙装备</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86"/>
+      <c r="L86"/>
+    </row>
+    <row r="87">
+      <c r="A87"/>
+      <c r="B87"/>
+      <c r="C87"/>
+      <c r="D87"/>
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="H87" t="str">
+        <v>Common</v>
+      </c>
+      <c r="I87" t="str">
+        <v>普通装备</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2</v>
+      </c>
+      <c r="K87"/>
+      <c r="L87"/>
+    </row>
+    <row r="88">
+      <c r="A88"/>
+      <c r="B88" t="str">
+        <v>Loot.PickupId</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88"/>
+      <c r="F88"/>
+      <c r="G88"/>
+      <c r="H88" t="str">
+        <v>None</v>
+      </c>
+      <c r="I88"/>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88"/>
+      <c r="L88"/>
+    </row>
+    <row r="89">
+      <c r="A89"/>
+      <c r="B89"/>
+      <c r="C89"/>
+      <c r="D89"/>
+      <c r="E89"/>
+      <c r="F89"/>
+      <c r="G89"/>
+      <c r="H89" t="str">
+        <v>SmallPeach</v>
+      </c>
+      <c r="I89"/>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89"/>
+      <c r="L89"/>
+    </row>
+    <row r="90">
+      <c r="A90"/>
+      <c r="B90"/>
+      <c r="C90"/>
+      <c r="D90"/>
+      <c r="E90"/>
+      <c r="F90"/>
+      <c r="G90"/>
+      <c r="H90" t="str">
+        <v>LargePeach</v>
+      </c>
+      <c r="I90"/>
+      <c r="J90" t="n">
+        <v>2</v>
+      </c>
+      <c r="K90"/>
+      <c r="L90"/>
+    </row>
+    <row r="91">
+      <c r="A91"/>
+      <c r="B91"/>
+      <c r="C91"/>
+      <c r="D91"/>
+      <c r="E91"/>
+      <c r="F91"/>
+      <c r="G91"/>
+      <c r="H91" t="str">
+        <v>ManaBottle</v>
+      </c>
+      <c r="I91"/>
+      <c r="J91" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91"/>
+      <c r="L91"/>
+    </row>
+    <row r="92">
+      <c r="A92"/>
+      <c r="B92" t="str">
+        <v>Loot.PickupEffect</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92"/>
+      <c r="F92"/>
+      <c r="G92"/>
+      <c r="H92" t="str">
+        <v>Health</v>
+      </c>
+      <c r="I92"/>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92"/>
+      <c r="L92"/>
+    </row>
+    <row r="93">
+      <c r="A93"/>
+      <c r="B93"/>
+      <c r="C93"/>
+      <c r="D93"/>
+      <c r="E93"/>
+      <c r="F93"/>
+      <c r="G93"/>
+      <c r="H93" t="str">
+        <v>Mana</v>
+      </c>
+      <c r="I93"/>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93"/>
+      <c r="L93"/>
+    </row>
+    <row r="94">
+      <c r="A94"/>
+      <c r="B94" t="str">
+        <v>Skills.SkillHero</v>
+      </c>
+      <c r="C94" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D94" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94"/>
+      <c r="F94"/>
+      <c r="G94"/>
+      <c r="H94" t="str">
+        <v>Wukong</v>
+      </c>
+      <c r="I94" t="str">
+        <v>悟空</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94"/>
+      <c r="L94"/>
+    </row>
+    <row r="95">
+      <c r="A95"/>
+      <c r="B95"/>
+      <c r="C95"/>
+      <c r="D95"/>
+      <c r="E95"/>
+      <c r="F95"/>
+      <c r="G95"/>
+      <c r="H95" t="str">
+        <v>Tangseng</v>
+      </c>
+      <c r="I95" t="str">
+        <v>唐僧</v>
+      </c>
+      <c r="J95" t="n">
+        <v>2</v>
+      </c>
+      <c r="K95"/>
+      <c r="L95"/>
+    </row>
+    <row r="96">
+      <c r="A96"/>
+      <c r="B96" t="str">
+        <v>Skills.SkillId</v>
+      </c>
+      <c r="C96" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D96" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96"/>
+      <c r="F96"/>
+      <c r="G96"/>
+      <c r="H96" t="str">
+        <v>RisingDragon</v>
+      </c>
+      <c r="I96" t="str">
+        <v>升龙斩</v>
+      </c>
+      <c r="J96" t="n">
+        <v>101</v>
+      </c>
+      <c r="K96"/>
+      <c r="L96"/>
+    </row>
+    <row r="97">
+      <c r="A97"/>
+      <c r="B97"/>
+      <c r="C97"/>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97"/>
+      <c r="G97"/>
+      <c r="H97" t="str">
+        <v>FlameThrust</v>
+      </c>
+      <c r="I97" t="str">
+        <v>火炎突击</v>
+      </c>
+      <c r="J97" t="n">
+        <v>102</v>
+      </c>
+      <c r="K97"/>
+      <c r="L97"/>
+    </row>
+    <row r="98">
+      <c r="A98"/>
+      <c r="B98"/>
+      <c r="C98"/>
+      <c r="D98"/>
+      <c r="E98"/>
+      <c r="F98"/>
+      <c r="G98"/>
+      <c r="H98" t="str">
+        <v>BlazingFlash</v>
+      </c>
+      <c r="I98" t="str">
+        <v>烈焰闪</v>
+      </c>
+      <c r="J98" t="n">
+        <v>103</v>
+      </c>
+      <c r="K98"/>
+      <c r="L98"/>
+    </row>
+    <row r="99">
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
+      <c r="G99"/>
+      <c r="H99" t="str">
+        <v>FlameStorm</v>
+      </c>
+      <c r="I99" t="str">
+        <v>烈焰风暴</v>
+      </c>
+      <c r="J99" t="n">
+        <v>104</v>
+      </c>
+      <c r="K99"/>
+      <c r="L99"/>
+    </row>
+    <row r="100">
+      <c r="A100"/>
+      <c r="B100"/>
+      <c r="C100"/>
+      <c r="D100"/>
+      <c r="E100"/>
+      <c r="F100"/>
+      <c r="G100"/>
+      <c r="H100" t="str">
+        <v>FireDemonSlash</v>
+      </c>
+      <c r="I100" t="str">
+        <v>火魔斩</v>
+      </c>
+      <c r="J100" t="n">
+        <v>105</v>
+      </c>
+      <c r="K100"/>
+      <c r="L100"/>
+    </row>
+    <row r="101">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101" t="str">
+        <v>IceDragonWave</v>
+      </c>
+      <c r="I101" t="str">
+        <v>冰龙波</v>
+      </c>
+      <c r="J101" t="n">
+        <v>201</v>
+      </c>
+      <c r="K101"/>
+      <c r="L101"/>
+    </row>
+    <row r="102">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102" t="str">
+        <v>DarkIceFormation</v>
+      </c>
+      <c r="I102" t="str">
+        <v>玄冰阵</v>
+      </c>
+      <c r="J102" t="n">
+        <v>202</v>
+      </c>
+      <c r="K102"/>
+      <c r="L102"/>
+    </row>
+    <row r="103">
+      <c r="A103"/>
+      <c r="B103"/>
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103"/>
+      <c r="H103" t="str">
+        <v>WaterClone</v>
+      </c>
+      <c r="I103" t="str">
+        <v>水幻影</v>
+      </c>
+      <c r="J103" t="n">
+        <v>203</v>
+      </c>
+      <c r="K103"/>
+      <c r="L103"/>
+    </row>
+    <row r="104">
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
+      <c r="H104" t="str">
+        <v>HeavenlyDew</v>
+      </c>
+      <c r="I104" t="str">
+        <v>天降甘露</v>
+      </c>
+      <c r="J104" t="n">
+        <v>204</v>
+      </c>
+      <c r="K104"/>
+      <c r="L104"/>
+    </row>
+    <row r="105">
+      <c r="A105"/>
+      <c r="B105"/>
+      <c r="C105"/>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
+      <c r="G105"/>
+      <c r="H105" t="str">
+        <v>WaterDemonBurst</v>
+      </c>
+      <c r="I105" t="str">
+        <v>水魔爆</v>
+      </c>
+      <c r="J105" t="n">
+        <v>205</v>
+      </c>
+      <c r="K105"/>
+      <c r="L105"/>
+    </row>
+    <row r="106">
+      <c r="A106"/>
+      <c r="B106" t="str">
+        <v>Skills.PassiveId</v>
+      </c>
+      <c r="C106" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D106" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E106"/>
+      <c r="F106"/>
+      <c r="G106"/>
+      <c r="H106" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="I106" t="str">
+        <v>热血</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106"/>
+      <c r="L106"/>
+    </row>
+    <row r="107">
+      <c r="A107"/>
+      <c r="B107"/>
+      <c r="C107"/>
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="H107" t="str">
+        <v>ManaSpring</v>
+      </c>
+      <c r="I107" t="str">
+        <v>魔泉</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107"/>
+      <c r="L107"/>
+    </row>
+    <row r="108">
+      <c r="A108"/>
+      <c r="B108"/>
+      <c r="C108"/>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
+      <c r="G108"/>
+      <c r="H108" t="str">
+        <v>Frenzy</v>
+      </c>
+      <c r="I108" t="str">
+        <v>狂暴</v>
+      </c>
+      <c r="J108" t="n">
+        <v>3</v>
+      </c>
+      <c r="K108"/>
+      <c r="L108"/>
+    </row>
+    <row r="109">
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+      <c r="D109"/>
+      <c r="E109"/>
+      <c r="F109"/>
+      <c r="G109"/>
+      <c r="H109" t="str">
+        <v>EternalLight</v>
+      </c>
+      <c r="I109" t="str">
+        <v>光之永恒</v>
+      </c>
+      <c r="J109" t="n">
+        <v>4</v>
+      </c>
+      <c r="K109"/>
+      <c r="L109"/>
+    </row>
+    <row r="110">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110"/>
+      <c r="G110"/>
+      <c r="H110" t="str">
+        <v>MoonBrilliance</v>
+      </c>
+      <c r="I110" t="str">
+        <v>月之辉煌</v>
+      </c>
+      <c r="J110" t="n">
+        <v>5</v>
+      </c>
+      <c r="K110"/>
+      <c r="L110"/>
+    </row>
+    <row r="111">
+      <c r="A111"/>
+      <c r="B111" t="str">
+        <v>Skills.PassiveEffect</v>
+      </c>
+      <c r="C111" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D111" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+      <c r="H111" t="str">
+        <v>MaxHealth</v>
+      </c>
+      <c r="I111" t="str">
+        <v>生命上限</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111"/>
+      <c r="L111"/>
+    </row>
+    <row r="112">
+      <c r="A112"/>
+      <c r="B112"/>
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112"/>
+      <c r="G112"/>
+      <c r="H112" t="str">
+        <v>MaxMana</v>
+      </c>
+      <c r="I112" t="str">
+        <v>魔法上限</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112"/>
+      <c r="L112"/>
+    </row>
+    <row r="113">
+      <c r="A113"/>
+      <c r="B113"/>
+      <c r="C113"/>
+      <c r="D113"/>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
+      <c r="H113" t="str">
+        <v>CriticalChance</v>
+      </c>
+      <c r="I113" t="str">
+        <v>暴击概率加成</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2</v>
+      </c>
+      <c r="K113"/>
+      <c r="L113"/>
+    </row>
+    <row r="114">
+      <c r="A114"/>
+      <c r="B114"/>
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
+      <c r="G114"/>
+      <c r="H114" t="str">
+        <v>HealthRegen</v>
+      </c>
+      <c r="I114" t="str">
+        <v>每秒回血</v>
+      </c>
+      <c r="J114" t="n">
+        <v>3</v>
+      </c>
+      <c r="K114"/>
+      <c r="L114"/>
+    </row>
+    <row r="115">
+      <c r="A115"/>
+      <c r="B115"/>
+      <c r="C115"/>
+      <c r="D115"/>
+      <c r="E115"/>
+      <c r="F115"/>
+      <c r="G115"/>
+      <c r="H115" t="str">
+        <v>ManaRegen</v>
+      </c>
+      <c r="I115" t="str">
+        <v>每秒回魔</v>
+      </c>
+      <c r="J115" t="n">
+        <v>4</v>
+      </c>
+      <c r="K115"/>
+      <c r="L115"/>
+    </row>
+    <row r="116">
+      <c r="A116"/>
+      <c r="B116" t="str">
+        <v>Skills.SkillHitId</v>
+      </c>
+      <c r="C116" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D116" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E116"/>
+      <c r="F116"/>
+      <c r="G116"/>
+      <c r="H116" t="str">
+        <v>None</v>
+      </c>
+      <c r="I116" t="str">
+        <v>无身体或特效伤害</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116"/>
+      <c r="L116"/>
+    </row>
+    <row r="117">
+      <c r="A117"/>
+      <c r="B117"/>
+      <c r="C117"/>
+      <c r="D117"/>
+      <c r="E117"/>
+      <c r="F117"/>
+      <c r="G117"/>
+      <c r="H117" t="str">
+        <v>RisingDragon</v>
+      </c>
+      <c r="I117" t="str">
+        <v>升龙斩</v>
+      </c>
+      <c r="J117" t="n">
+        <v>101</v>
+      </c>
+      <c r="K117"/>
+      <c r="L117"/>
+    </row>
+    <row r="118">
+      <c r="A118"/>
+      <c r="B118"/>
+      <c r="C118"/>
+      <c r="D118"/>
+      <c r="E118"/>
+      <c r="F118"/>
+      <c r="G118"/>
+      <c r="H118" t="str">
+        <v>FlameThrust</v>
+      </c>
+      <c r="I118" t="str">
+        <v>火炎突击</v>
+      </c>
+      <c r="J118" t="n">
+        <v>102</v>
+      </c>
+      <c r="K118"/>
+      <c r="L118"/>
+    </row>
+    <row r="119">
+      <c r="A119"/>
+      <c r="B119"/>
+      <c r="C119"/>
+      <c r="D119"/>
+      <c r="E119"/>
+      <c r="F119"/>
+      <c r="G119"/>
+      <c r="H119" t="str">
+        <v>BlazingFlash</v>
+      </c>
+      <c r="I119" t="str">
+        <v>烈焰闪</v>
+      </c>
+      <c r="J119" t="n">
+        <v>103</v>
+      </c>
+      <c r="K119"/>
+      <c r="L119"/>
+    </row>
+    <row r="120">
+      <c r="A120"/>
+      <c r="B120"/>
+      <c r="C120"/>
+      <c r="D120"/>
+      <c r="E120"/>
+      <c r="F120"/>
+      <c r="G120"/>
+      <c r="H120" t="str">
+        <v>FlameStorm</v>
+      </c>
+      <c r="I120" t="str">
+        <v>烈焰风暴</v>
+      </c>
+      <c r="J120" t="n">
+        <v>104</v>
+      </c>
+      <c r="K120"/>
+      <c r="L120"/>
+    </row>
+    <row r="121">
+      <c r="A121"/>
+      <c r="B121"/>
+      <c r="C121"/>
+      <c r="D121"/>
+      <c r="E121"/>
+      <c r="F121"/>
+      <c r="G121"/>
+      <c r="H121" t="str">
+        <v>FireDemonCombo</v>
+      </c>
+      <c r="I121" t="str">
+        <v>火魔九连斩</v>
+      </c>
+      <c r="J121" t="n">
+        <v>105</v>
+      </c>
+      <c r="K121"/>
+      <c r="L121"/>
+    </row>
+    <row r="122">
+      <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122"/>
+      <c r="D122"/>
+      <c r="E122"/>
+      <c r="F122"/>
+      <c r="G122"/>
+      <c r="H122" t="str">
+        <v>FireDemonDescent</v>
+      </c>
+      <c r="I122" t="str">
+        <v>火魔下冲</v>
+      </c>
+      <c r="J122" t="n">
+        <v>106</v>
+      </c>
+      <c r="K122"/>
+      <c r="L122"/>
+    </row>
+    <row r="123">
+      <c r="A123"/>
+      <c r="B123"/>
+      <c r="C123"/>
+      <c r="D123"/>
+      <c r="E123"/>
+      <c r="F123"/>
+      <c r="G123"/>
+      <c r="H123" t="str">
+        <v>FireDemonLanding</v>
+      </c>
+      <c r="I123" t="str">
+        <v>火魔落地斩</v>
+      </c>
+      <c r="J123" t="n">
+        <v>107</v>
+      </c>
+      <c r="K123"/>
+      <c r="L123"/>
+    </row>
+    <row r="124">
+      <c r="A124"/>
+      <c r="B124"/>
+      <c r="C124"/>
+      <c r="D124"/>
+      <c r="E124"/>
+      <c r="F124"/>
+      <c r="G124"/>
+      <c r="H124" t="str">
+        <v>IceDragonWave</v>
+      </c>
+      <c r="I124" t="str">
+        <v>冰龙波</v>
+      </c>
+      <c r="J124" t="n">
+        <v>201</v>
+      </c>
+      <c r="K124"/>
+      <c r="L124"/>
+    </row>
+    <row r="125">
+      <c r="A125"/>
+      <c r="B125"/>
+      <c r="C125"/>
+      <c r="D125"/>
+      <c r="E125"/>
+      <c r="F125"/>
+      <c r="G125"/>
+      <c r="H125" t="str">
+        <v>DarkIceFormation</v>
+      </c>
+      <c r="I125" t="str">
+        <v>玄冰阵</v>
+      </c>
+      <c r="J125" t="n">
+        <v>202</v>
+      </c>
+      <c r="K125"/>
+      <c r="L125"/>
+    </row>
+    <row r="126">
+      <c r="A126"/>
+      <c r="B126"/>
+      <c r="C126"/>
+      <c r="D126"/>
+      <c r="E126"/>
+      <c r="F126"/>
+      <c r="G126"/>
+      <c r="H126" t="str">
+        <v>WaterDemonPillar</v>
+      </c>
+      <c r="I126" t="str">
+        <v>水魔光柱</v>
+      </c>
+      <c r="J126" t="n">
+        <v>203</v>
+      </c>
+      <c r="K126"/>
+      <c r="L126"/>
+    </row>
+    <row r="127">
+      <c r="A127"/>
+      <c r="B127"/>
+      <c r="C127"/>
+      <c r="D127"/>
+      <c r="E127"/>
+      <c r="F127"/>
+      <c r="G127"/>
+      <c r="H127" t="str">
+        <v>WaterDemonFall</v>
+      </c>
+      <c r="I127" t="str">
+        <v>水魔追加下落</v>
+      </c>
+      <c r="J127" t="n">
+        <v>204</v>
+      </c>
+      <c r="K127"/>
+      <c r="L127"/>
+    </row>
+    <row r="128">
+      <c r="A128"/>
+      <c r="B128" t="str">
+        <v>Skills.SkillPowerRounding</v>
+      </c>
+      <c r="C128" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D128" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E128"/>
+      <c r="F128"/>
+      <c r="G128"/>
+      <c r="H128" t="str">
+        <v>None</v>
+      </c>
+      <c r="I128" t="str">
+        <v>保持小数到最终转int</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128"/>
+      <c r="L128"/>
+    </row>
+    <row r="129">
+      <c r="A129"/>
+      <c r="B129"/>
+      <c r="C129"/>
+      <c r="D129"/>
+      <c r="E129"/>
+      <c r="F129"/>
+      <c r="G129"/>
+      <c r="H129" t="str">
+        <v>BeforeScale</v>
+      </c>
+      <c r="I129" t="str">
+        <v>先按Math.round舍入攻击力再乘倍率</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129"/>
+      <c r="L129"/>
+    </row>
+    <row r="130">
+      <c r="A130"/>
+      <c r="B130"/>
+      <c r="C130"/>
+      <c r="D130"/>
+      <c r="E130"/>
+      <c r="F130"/>
+      <c r="G130"/>
+      <c r="H130" t="str">
+        <v>AfterScale</v>
+      </c>
+      <c r="I130" t="str">
+        <v>倍率后按Math.round舍入</v>
+      </c>
+      <c r="J130" t="n">
+        <v>2</v>
+      </c>
+      <c r="K130"/>
+      <c r="L130"/>
+    </row>
+    <row r="131">
+      <c r="A131"/>
+      <c r="B131" t="str">
+        <v>Skills.SkillEffectId</v>
+      </c>
+      <c r="C131" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D131" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E131"/>
+      <c r="F131"/>
+      <c r="G131"/>
+      <c r="H131" t="str">
+        <v>None</v>
+      </c>
+      <c r="I131" t="str">
+        <v>无独立特效</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131"/>
+      <c r="L131"/>
+    </row>
+    <row r="132">
+      <c r="A132"/>
+      <c r="B132"/>
+      <c r="C132"/>
+      <c r="D132"/>
+      <c r="E132"/>
+      <c r="F132"/>
+      <c r="G132"/>
+      <c r="H132" t="str">
+        <v>BlazingFlashTrail</v>
+      </c>
+      <c r="I132" t="str">
+        <v>烈焰闪余焰</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132"/>
+      <c r="L132"/>
+    </row>
+    <row r="133">
+      <c r="A133"/>
+      <c r="B133"/>
+      <c r="C133"/>
+      <c r="D133"/>
+      <c r="E133"/>
+      <c r="F133"/>
+      <c r="G133"/>
+      <c r="H133" t="str">
+        <v>FireDemonPrelude</v>
+      </c>
+      <c r="I133" t="str">
+        <v>火魔起手光效</v>
+      </c>
+      <c r="J133" t="n">
+        <v>2</v>
+      </c>
+      <c r="K133"/>
+      <c r="L133"/>
+    </row>
+    <row r="134">
+      <c r="A134"/>
+      <c r="B134"/>
+      <c r="C134"/>
+      <c r="D134"/>
+      <c r="E134"/>
+      <c r="F134"/>
+      <c r="G134"/>
+      <c r="H134" t="str">
+        <v>FireDemonCombo</v>
+      </c>
+      <c r="I134" t="str">
+        <v>火魔九连斩</v>
+      </c>
+      <c r="J134" t="n">
+        <v>3</v>
+      </c>
+      <c r="K134"/>
+      <c r="L134"/>
+    </row>
+    <row r="135">
+      <c r="A135"/>
+      <c r="B135"/>
+      <c r="C135"/>
+      <c r="D135"/>
+      <c r="E135"/>
+      <c r="F135"/>
+      <c r="G135"/>
+      <c r="H135" t="str">
+        <v>FireDemonDescent</v>
+      </c>
+      <c r="I135" t="str">
+        <v>火魔下冲</v>
+      </c>
+      <c r="J135" t="n">
+        <v>4</v>
+      </c>
+      <c r="K135"/>
+      <c r="L135"/>
+    </row>
+    <row r="136">
+      <c r="A136"/>
+      <c r="B136"/>
+      <c r="C136"/>
+      <c r="D136"/>
+      <c r="E136"/>
+      <c r="F136"/>
+      <c r="G136"/>
+      <c r="H136" t="str">
+        <v>FireDemonLanding</v>
+      </c>
+      <c r="I136" t="str">
+        <v>火魔落地斩</v>
+      </c>
+      <c r="J136" t="n">
+        <v>5</v>
+      </c>
+      <c r="K136"/>
+      <c r="L136"/>
+    </row>
+    <row r="137">
+      <c r="A137"/>
+      <c r="B137" t="str">
+        <v>Skills.SkillEffectMirror</v>
+      </c>
+      <c r="C137" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D137" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E137"/>
+      <c r="F137"/>
+      <c r="G137"/>
+      <c r="H137" t="str">
+        <v>Actor</v>
+      </c>
+      <c r="I137" t="str">
+        <v>与源角色矩阵一致</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137"/>
+      <c r="L137"/>
+    </row>
+    <row r="138">
+      <c r="A138"/>
+      <c r="B138"/>
+      <c r="C138"/>
+      <c r="D138"/>
+      <c r="E138"/>
+      <c r="F138"/>
+      <c r="G138"/>
+      <c r="H138" t="str">
+        <v>OppositeActor</v>
+      </c>
+      <c r="I138" t="str">
+        <v>与源角色矩阵相反</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138"/>
+      <c r="L138"/>
+    </row>
+    <row r="139">
+      <c r="A139"/>
+      <c r="B139"/>
+      <c r="C139"/>
+      <c r="D139"/>
+      <c r="E139"/>
+      <c r="F139"/>
+      <c r="G139"/>
+      <c r="H139"/>
+      <c r="I139"/>
+      <c r="J139"/>
+      <c r="K139"/>
+      <c r="L139"/>
+    </row>
+    <row r="140">
+      <c r="A140"/>
+      <c r="B140" t="str">
+        <v>Skills.SkillTimelineKind</v>
+      </c>
+      <c r="C140" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D140" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E140"/>
+      <c r="F140"/>
+      <c r="G140"/>
+      <c r="H140" t="str">
+        <v>NewAttackId</v>
+      </c>
+      <c r="I140" t="str">
+        <v>更新当前时间轴所属攻击编号</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140"/>
+      <c r="L140"/>
+    </row>
+    <row r="141">
+      <c r="A141"/>
+      <c r="B141"/>
+      <c r="C141"/>
+      <c r="D141"/>
+      <c r="E141"/>
+      <c r="F141"/>
+      <c r="G141"/>
+      <c r="H141" t="str">
+        <v>SetVelocityX</v>
+      </c>
+      <c r="I141" t="str">
+        <v>只设置水平速度</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141"/>
+      <c r="L141"/>
+    </row>
+    <row r="142">
+      <c r="A142"/>
+      <c r="B142"/>
+      <c r="C142"/>
+      <c r="D142"/>
+      <c r="E142"/>
+      <c r="F142"/>
+      <c r="G142"/>
+      <c r="H142" t="str">
+        <v>SetVelocity</v>
+      </c>
+      <c r="I142" t="str">
+        <v>设置两轴速度</v>
+      </c>
+      <c r="J142" t="n">
+        <v>2</v>
+      </c>
+      <c r="K142"/>
+      <c r="L142"/>
+    </row>
+    <row r="143">
+      <c r="A143"/>
+      <c r="B143"/>
+      <c r="C143"/>
+      <c r="D143"/>
+      <c r="E143"/>
+      <c r="F143"/>
+      <c r="G143"/>
+      <c r="H143" t="str">
+        <v>MultiplyVelocityX</v>
+      </c>
+      <c r="I143" t="str">
+        <v>水平速度乘系数</v>
+      </c>
+      <c r="J143" t="n">
+        <v>3</v>
+      </c>
+      <c r="K143"/>
+      <c r="L143"/>
+    </row>
+    <row r="144">
+      <c r="A144"/>
+      <c r="B144"/>
+      <c r="C144"/>
+      <c r="D144"/>
+      <c r="E144"/>
+      <c r="F144"/>
+      <c r="G144"/>
+      <c r="H144" t="str">
+        <v>SpawnEffect</v>
+      </c>
+      <c r="I144" t="str">
+        <v>创建指定特效</v>
+      </c>
+      <c r="J144" t="n">
+        <v>4</v>
+      </c>
+      <c r="K144"/>
+      <c r="L144"/>
+    </row>
+    <row r="145">
+      <c r="A145"/>
+      <c r="B145"/>
+      <c r="C145"/>
+      <c r="D145"/>
+      <c r="E145"/>
+      <c r="F145"/>
+      <c r="G145"/>
+      <c r="H145" t="str">
+        <v>StopMotion</v>
+      </c>
+      <c r="I145" t="str">
+        <v>两轴速度归零</v>
+      </c>
+      <c r="J145" t="n">
+        <v>5</v>
+      </c>
+      <c r="K145"/>
+      <c r="L145"/>
+    </row>
+    <row r="146">
+      <c r="A146"/>
+      <c r="B146"/>
+      <c r="C146"/>
+      <c r="D146"/>
+      <c r="E146"/>
+      <c r="F146"/>
+      <c r="G146"/>
+      <c r="H146" t="str">
+        <v>SuspendGravityAndInput</v>
+      </c>
+      <c r="I146" t="str">
+        <v>禁重力和键盘</v>
+      </c>
+      <c r="J146" t="n">
+        <v>6</v>
+      </c>
+      <c r="K146"/>
+      <c r="L146"/>
+    </row>
+    <row r="147">
+      <c r="A147"/>
+      <c r="B147"/>
+      <c r="C147"/>
+      <c r="D147"/>
+      <c r="E147"/>
+      <c r="F147"/>
+      <c r="G147"/>
+      <c r="H147" t="str">
+        <v>SearchTarget</v>
+      </c>
+      <c r="I147" t="str">
+        <v>按可见碰撞左缘及欧氏距离取首个目标</v>
+      </c>
+      <c r="J147" t="n">
+        <v>7</v>
+      </c>
+      <c r="K147"/>
+      <c r="L147"/>
+    </row>
+    <row r="148">
+      <c r="A148"/>
+      <c r="B148"/>
+      <c r="C148"/>
+      <c r="D148"/>
+      <c r="E148"/>
+      <c r="F148"/>
+      <c r="G148"/>
+      <c r="H148" t="str">
+        <v>TeleportToTarget</v>
+      </c>
+      <c r="I148" t="str">
+        <v>定位到搜索目标</v>
+      </c>
+      <c r="J148" t="n">
+        <v>8</v>
+      </c>
+      <c r="K148"/>
+      <c r="L148"/>
+    </row>
+    <row r="149">
+      <c r="A149"/>
+      <c r="B149"/>
+      <c r="C149"/>
+      <c r="D149"/>
+      <c r="E149"/>
+      <c r="F149"/>
+      <c r="G149"/>
+      <c r="H149" t="str">
+        <v>SeekActor</v>
+      </c>
+      <c r="I149" t="str">
+        <v>跳转角色时间轴并处理目标时点事件</v>
+      </c>
+      <c r="J149" t="n">
+        <v>9</v>
+      </c>
+      <c r="K149"/>
+      <c r="L149"/>
+    </row>
+    <row r="150">
+      <c r="A150"/>
+      <c r="B150"/>
+      <c r="C150"/>
+      <c r="D150"/>
+      <c r="E150"/>
+      <c r="F150"/>
+      <c r="G150"/>
+      <c r="H150" t="str">
+        <v>SpawnLandingAndPauseActor</v>
+      </c>
+      <c r="I150" t="str">
+        <v>首次落地创建特效并暂停角色动作</v>
+      </c>
+      <c r="J150" t="n">
+        <v>10</v>
+      </c>
+      <c r="K150"/>
+      <c r="L150"/>
+    </row>
+    <row r="151">
+      <c r="A151"/>
+      <c r="B151"/>
+      <c r="C151"/>
+      <c r="D151"/>
+      <c r="E151"/>
+      <c r="F151"/>
+      <c r="G151"/>
+      <c r="H151" t="str">
+        <v>RestoreGravityAndInput</v>
+      </c>
+      <c r="I151" t="str">
+        <v>恢复重力和键盘</v>
+      </c>
+      <c r="J151" t="n">
+        <v>11</v>
+      </c>
+      <c r="K151"/>
+      <c r="L151"/>
+    </row>
+    <row r="152">
+      <c r="A152"/>
+      <c r="B152"/>
+      <c r="C152"/>
+      <c r="D152"/>
+      <c r="E152"/>
+      <c r="F152"/>
+      <c r="G152"/>
+      <c r="H152" t="str">
+        <v>CompleteActor</v>
+      </c>
+      <c r="I152" t="str">
+        <v>按地空及输入结束技能</v>
+      </c>
+      <c r="J152" t="n">
+        <v>12</v>
+      </c>
+      <c r="K152"/>
+      <c r="L152"/>
+    </row>
+    <row r="153">
+      <c r="A153"/>
+      <c r="B153"/>
+      <c r="C153"/>
+      <c r="D153"/>
+      <c r="E153"/>
+      <c r="F153"/>
+      <c r="G153"/>
+      <c r="H153" t="str">
+        <v>CompleteEffect</v>
+      </c>
+      <c r="I153" t="str">
+        <v>结束所属独立特效</v>
+      </c>
+      <c r="J153" t="n">
+        <v>13</v>
+      </c>
+      <c r="K153"/>
+      <c r="L153"/>
+    </row>
+    <row r="154">
+      <c r="A154"/>
+      <c r="B154"/>
+      <c r="C154"/>
+      <c r="D154"/>
+      <c r="E154"/>
+      <c r="F154"/>
+      <c r="G154"/>
+      <c r="H154" t="str">
+        <v>FinishLandingEffect</v>
+      </c>
+      <c r="I154" t="str">
+        <v>角色转结束帧后结束落地特效</v>
+      </c>
+      <c r="J154" t="n">
+        <v>14</v>
+      </c>
+      <c r="K154"/>
+      <c r="L154"/>
+    </row>
+    <row r="155">
+      <c r="A155"/>
+      <c r="B155" t="str">
+        <v>Skills.SkillTimelineCondition</v>
+      </c>
+      <c r="C155" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D155" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E155"/>
+      <c r="F155"/>
+      <c r="G155"/>
+      <c r="H155" t="str">
+        <v>Always</v>
+      </c>
+      <c r="I155" t="str">
+        <v>无条件</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155"/>
+      <c r="L155"/>
+    </row>
+    <row r="156">
+      <c r="A156"/>
+      <c r="B156"/>
+      <c r="C156"/>
+      <c r="D156"/>
+      <c r="E156"/>
+      <c r="F156"/>
+      <c r="G156"/>
+      <c r="H156" t="str">
+        <v>TargetFound</v>
+      </c>
+      <c r="I156" t="str">
+        <v>本次搜索命中目标</v>
+      </c>
+      <c r="J156" t="n">
+        <v>1</v>
+      </c>
+      <c r="K156"/>
+      <c r="L156"/>
+    </row>
+    <row r="157">
+      <c r="A157"/>
+      <c r="B157"/>
+      <c r="C157"/>
+      <c r="D157"/>
+      <c r="E157"/>
+      <c r="F157"/>
+      <c r="G157"/>
+      <c r="H157" t="str">
+        <v>TargetMissing</v>
+      </c>
+      <c r="I157" t="str">
+        <v>本次搜索未命中目标</v>
+      </c>
+      <c r="J157" t="n">
+        <v>2</v>
+      </c>
+      <c r="K157"/>
+      <c r="L157"/>
+    </row>
+    <row r="158">
+      <c r="A158"/>
+      <c r="B158"/>
+      <c r="C158"/>
+      <c r="D158"/>
+      <c r="E158"/>
+      <c r="F158"/>
+      <c r="G158"/>
+      <c r="H158" t="str">
+        <v>OnFloor</v>
+      </c>
+      <c r="I158" t="str">
+        <v>角色踩地或平台且尚未创建落地特效</v>
+      </c>
+      <c r="J158" t="n">
+        <v>3</v>
+      </c>
+      <c r="K158"/>
+      <c r="L158"/>
+    </row>
+    <row r="159">
+      <c r="A159"/>
+      <c r="B159"/>
+      <c r="C159"/>
+      <c r="D159"/>
+      <c r="E159"/>
+      <c r="F159"/>
+      <c r="G159"/>
+      <c r="H159" t="str">
+        <v>LandingMissing</v>
+      </c>
+      <c r="I159" t="str">
+        <v>本次技能尚未创建落地特效</v>
+      </c>
+      <c r="J159" t="n">
+        <v>4</v>
+      </c>
+      <c r="K159"/>
+      <c r="L159"/>
+    </row>
+    <row r="160">
+      <c r="A160"/>
+      <c r="B160" t="str">
+        <v>Skills.SkillMotionDirection</v>
+      </c>
+      <c r="C160" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D160" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E160"/>
+      <c r="F160"/>
+      <c r="G160"/>
+      <c r="H160" t="str">
+        <v>Actor</v>
+      </c>
+      <c r="I160" t="str">
+        <v>横向按角色朝向</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160"/>
+      <c r="L160"/>
+    </row>
+    <row r="161">
+      <c r="A161"/>
+      <c r="B161"/>
+      <c r="C161"/>
+      <c r="D161"/>
+      <c r="E161"/>
+      <c r="F161"/>
+      <c r="G161"/>
+      <c r="H161" t="str">
+        <v>ExistingVelocity</v>
+      </c>
+      <c r="I161" t="str">
+        <v>沿原水平速度；零按原版取负</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K161"/>
+      <c r="L161"/>
+    </row>
+    <row r="162">
+      <c r="A162"/>
+      <c r="B162" t="str">
+        <v>Skills.SkillEffectAnchor</v>
+      </c>
+      <c r="C162" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D162" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E162"/>
+      <c r="F162"/>
+      <c r="G162"/>
+      <c r="H162" t="str">
+        <v>Actor</v>
+      </c>
+      <c r="I162" t="str">
+        <v>角色当前坐标</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162"/>
+      <c r="L162"/>
+    </row>
+    <row r="163">
+      <c r="A163"/>
+      <c r="B163"/>
+      <c r="C163"/>
+      <c r="D163"/>
+      <c r="E163"/>
+      <c r="F163"/>
+      <c r="G163"/>
+      <c r="H163" t="str">
+        <v>SelectedTarget</v>
+      </c>
+      <c r="I163" t="str">
+        <v>选中目标坐标</v>
+      </c>
+      <c r="J163" t="n">
+        <v>1</v>
+      </c>
+      <c r="K163"/>
+      <c r="L163"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1213,7 +1213,7 @@
     <row r="5">
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">BattleHud</t>
+          <t>BattleForm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R37091f04a88c4444"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02b1ab4c8ca4455c"/>
   </sheets>
 </workbook>
 </file>
@@ -772,26 +772,22 @@
     </row>
     <row r="20" ht="14" customHeight="1">
       <c r="A20" s="6"/>
-      <c r="B20" s="6" t="str">
-        <v>Battle.DamageKind</v>
-      </c>
-      <c r="C20" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" s="8" t="b">
-        <v>1</v>
-      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="6" t="str">
-        <v>Physics</v>
+        <v>MacaqueKing</v>
       </c>
       <c r="I20" s="6" t="str">
-        <v>物理</v>
-      </c>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
+        <v>猕猴王</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="6"/>
       <c r="L20" s="6"/>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -803,28 +799,36 @@
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="6" t="str">
-        <v>Magic</v>
+        <v>TamarinKing</v>
       </c>
       <c r="I21" s="6" t="str">
-        <v>魔法</v>
-      </c>
-      <c r="J21" s="7"/>
+        <v>禺狨王</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>6</v>
+      </c>
       <c r="K21" s="7"/>
       <c r="L21" s="6"/>
     </row>
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="B22" s="6" t="str">
+        <v>Battle.DamageKind</v>
+      </c>
+      <c r="C22" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="8" t="b">
+        <v>1</v>
+      </c>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="6" t="str">
-        <v>Real</v>
+        <v>Physics</v>
       </c>
       <c r="I22" s="6" t="str">
-        <v>真实</v>
+        <v>物理</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -832,27 +836,19 @@
     </row>
     <row r="23" ht="14" customHeight="1">
       <c r="A23" s="6"/>
-      <c r="B23" s="6" t="str">
-        <v>Sound.SoundId</v>
-      </c>
-      <c r="C23" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="8" t="b">
-        <v>1</v>
-      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="6" t="str">
-        <v>None</v>
+        <v>Magic</v>
       </c>
       <c r="I23" s="6" t="str">
-        <v>无</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0</v>
-      </c>
+        <v>魔法</v>
+      </c>
+      <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="6"/>
     </row>
@@ -865,33 +861,37 @@
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
       <c r="H24" s="6" t="str">
-        <v>WukongAttack1And2</v>
+        <v>Real</v>
       </c>
       <c r="I24" s="6" t="str">
-        <v>悟空挥棍1/2</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>1</v>
-      </c>
+        <v>真实</v>
+      </c>
+      <c r="J24" s="7"/>
       <c r="K24" s="7"/>
       <c r="L24" s="6"/>
     </row>
     <row r="25" ht="14" customHeight="1">
       <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
+      <c r="B25" s="6" t="str">
+        <v>Sound.SoundId</v>
+      </c>
+      <c r="C25" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="8" t="b">
+        <v>1</v>
+      </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="6" t="str">
-        <v>WukongAttack3And4</v>
+        <v>None</v>
       </c>
       <c r="I25" s="6" t="str">
-        <v>悟空挥棍3/4</v>
+        <v>无</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="6"/>
@@ -905,13 +905,13 @@
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
       <c r="H26" s="6" t="str">
-        <v>WukongAttack5</v>
+        <v>WukongAttack1And2</v>
       </c>
       <c r="I26" s="6" t="str">
-        <v>悟空挥棍5</v>
+        <v>悟空挥棍1/2</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="6"/>
@@ -925,13 +925,13 @@
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="6" t="str">
-        <v>WukongHurt</v>
+        <v>WukongAttack3And4</v>
       </c>
       <c r="I27" s="6" t="str">
-        <v>悟空受击语音</v>
+        <v>悟空挥棍3/4</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="6"/>
@@ -945,13 +945,13 @@
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="6" t="str">
-        <v>WukongDeath</v>
+        <v>WukongAttack5</v>
       </c>
       <c r="I28" s="6" t="str">
-        <v>悟空死亡语音</v>
+        <v>悟空挥棍5</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="6"/>
@@ -965,13 +965,13 @@
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="6" t="str">
-        <v>WukongImpact</v>
+        <v>WukongHurt</v>
       </c>
       <c r="I29" s="6" t="str">
-        <v>悟空命中音(棍打中东西)</v>
+        <v>悟空受击语音</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="6"/>
@@ -985,13 +985,13 @@
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="6" t="str">
-        <v>MenuTheme</v>
+        <v>WukongDeath</v>
       </c>
       <c r="I30" s="6" t="str">
-        <v>开始与选角音乐</v>
+        <v>悟空死亡语音</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="6"/>
@@ -1005,13 +1005,13 @@
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="6" t="str">
-        <v>MapTheme</v>
+        <v>WukongImpact</v>
       </c>
       <c r="I31" s="6" t="str">
-        <v>地图音乐</v>
+        <v>悟空命中音(棍打中东西)</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>101</v>
+        <v>6</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="6"/>
@@ -1025,13 +1025,13 @@
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="6" t="str">
-        <v>HuaguoshanTheme</v>
+        <v>MenuTheme</v>
       </c>
       <c r="I32" s="6" t="str">
-        <v>花果山音乐</v>
+        <v>开始与选角音乐</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="6"/>
@@ -1045,13 +1045,13 @@
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="6" t="str">
-        <v>MenuConfirm</v>
+        <v>MapTheme</v>
       </c>
       <c r="I33" s="6" t="str">
-        <v>菜单确认音</v>
+        <v>地图音乐</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="6"/>
@@ -1065,13 +1065,13 @@
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="H34" s="6" t="str">
-        <v>WukongRisingDragon</v>
+        <v>HuaguoshanTheme</v>
       </c>
       <c r="I34" s="6" t="str">
-        <v>悟空升龙斩</v>
+        <v>花果山音乐</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>7</v>
+        <v>102</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="6"/>
@@ -1085,13 +1085,13 @@
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="6" t="str">
-        <v>WukongFlameThrust</v>
+        <v>MenuConfirm</v>
       </c>
       <c r="I35" s="6" t="str">
-        <v>悟空火炎突击</v>
+        <v>菜单确认音</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="6"/>
@@ -1105,13 +1105,13 @@
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="6" t="str">
-        <v>WukongBlazingFlash</v>
+        <v>WukongRisingDragon</v>
       </c>
       <c r="I36" s="6" t="str">
-        <v>悟空烈焰闪</v>
+        <v>悟空升龙斩</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="6"/>
@@ -1125,13 +1125,13 @@
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="6" t="str">
-        <v>WukongFlameStorm</v>
+        <v>WukongFlameThrust</v>
       </c>
       <c r="I37" s="6" t="str">
-        <v>悟空烈焰风暴</v>
+        <v>悟空火炎突击</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="6"/>
@@ -1145,13 +1145,13 @@
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
       <c r="H38" s="6" t="str">
-        <v>WukongFireDemonStart</v>
+        <v>WukongBlazingFlash</v>
       </c>
       <c r="I38" s="6" t="str">
-        <v>悟空火魔斩起手</v>
+        <v>悟空烈焰闪</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="6"/>
@@ -1165,13 +1165,13 @@
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
       <c r="H39" s="6" t="str">
-        <v>WukongFireDemonCombo</v>
+        <v>WukongFlameStorm</v>
       </c>
       <c r="I39" s="6" t="str">
-        <v>悟空火魔九连斩</v>
+        <v>悟空烈焰风暴</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="6"/>
@@ -1185,39 +1185,33 @@
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="6" t="str">
-        <v>WukongFireDemonLanding</v>
+        <v>WukongFireDemonStart</v>
       </c>
       <c r="I40" s="6" t="str">
-        <v>悟空火魔斩落地</v>
+        <v>悟空火魔斩起手</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="6"/>
     </row>
     <row r="41" ht="14" customHeight="1">
       <c r="A41" s="6"/>
-      <c r="B41" s="6" t="str">
-        <v>Level.StageActivation</v>
-      </c>
-      <c r="C41" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D41" s="8" t="b">
-        <v>1</v>
-      </c>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="6" t="str">
-        <v>CameraArrived</v>
+        <v>WukongFireDemonCombo</v>
       </c>
       <c r="I41" s="6" t="str">
-        <v>相机抵达阶段右界</v>
+        <v>悟空火魔九连斩</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="6"/>
@@ -1231,39 +1225,33 @@
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="6" t="str">
-        <v>Trigger</v>
+        <v>WukongFireDemonLanding</v>
       </c>
       <c r="I42" s="6" t="str">
-        <v>特殊区域激活</v>
+        <v>悟空火魔斩落地</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="6"/>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="6"/>
-      <c r="B43" s="6" t="str">
-        <v>Attributes.AttributeType</v>
-      </c>
-      <c r="C43" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D43" s="8" t="b">
-        <v>1</v>
-      </c>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
       <c r="H43" s="6" t="str">
-        <v>MaxHp</v>
+        <v>SettlementVictory</v>
       </c>
       <c r="I43" s="6" t="str">
-        <v>生命上限</v>
+        <v>挑战成功音乐</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="6"/>
@@ -1277,33 +1265,39 @@
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="6" t="str">
-        <v>MaxMp</v>
+        <v>SettlementDefeat</v>
       </c>
       <c r="I44" s="6" t="str">
-        <v>魔法上限</v>
+        <v>挑战失败音乐</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="6"/>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="6"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
+      <c r="B45" s="6" t="str">
+        <v>Level.StageActivation</v>
+      </c>
+      <c r="C45" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" s="8" t="b">
+        <v>1</v>
+      </c>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
       <c r="H45" s="6" t="str">
-        <v>Power</v>
+        <v>CameraArrived</v>
       </c>
       <c r="I45" s="6" t="str">
-        <v>攻击</v>
+        <v>相机抵达阶段右界</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="6"/>
@@ -1317,33 +1311,39 @@
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
       <c r="H46" s="6" t="str">
-        <v>Def</v>
+        <v>Trigger</v>
       </c>
       <c r="I46" s="6" t="str">
-        <v>物防</v>
+        <v>特殊区域激活</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="6"/>
     </row>
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="6"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
+      <c r="B47" s="6" t="str">
+        <v>Attributes.AttributeType</v>
+      </c>
+      <c r="C47" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" s="8" t="b">
+        <v>1</v>
+      </c>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
       <c r="H47" s="6" t="str">
-        <v>Mdef</v>
+        <v>MaxHp</v>
       </c>
       <c r="I47" s="6" t="str">
-        <v>魔防</v>
+        <v>生命上限</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="6"/>
@@ -1357,13 +1357,13 @@
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
       <c r="H48" s="6" t="str">
-        <v>Crit</v>
+        <v>MaxMp</v>
       </c>
       <c r="I48" s="6" t="str">
-        <v>暴击</v>
+        <v>魔法上限</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="6"/>
@@ -1377,13 +1377,13 @@
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
       <c r="H49" s="6" t="str">
-        <v>Miss</v>
+        <v>Power</v>
       </c>
       <c r="I49" s="6" t="str">
-        <v>闪避</v>
+        <v>攻击</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="6"/>
@@ -1397,13 +1397,13 @@
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
       <c r="H50" s="6" t="str">
-        <v>Lucky</v>
+        <v>Def</v>
       </c>
       <c r="I50" s="6" t="str">
-        <v>幸运(加暴击倍率)</v>
+        <v>物防</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="6"/>
@@ -1417,13 +1417,13 @@
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
       <c r="H51" s="6" t="str">
-        <v>Toughness</v>
+        <v>Mdef</v>
       </c>
       <c r="I51" s="6" t="str">
-        <v>韧性(减对方幸运)</v>
+        <v>魔防</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="6"/>
@@ -1437,13 +1437,13 @@
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
       <c r="H52" s="6" t="str">
-        <v>Htarget</v>
+        <v>Crit</v>
       </c>
       <c r="I52" s="6" t="str">
-        <v>命中(减对方闪避)</v>
+        <v>暴击</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="6"/>
@@ -1457,13 +1457,13 @@
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
       <c r="H53" s="6" t="str">
-        <v>CritReduce</v>
+        <v>Miss</v>
       </c>
       <c r="I53" s="6" t="str">
-        <v>暴击抵抗</v>
+        <v>闪避</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="6"/>
@@ -1477,13 +1477,13 @@
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
       <c r="H54" s="6" t="str">
-        <v>Ar</v>
+        <v>Lucky</v>
       </c>
       <c r="I54" s="6" t="str">
-        <v>破甲(减对方物防)</v>
+        <v>幸运(加暴击倍率)</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="6"/>
@@ -1497,13 +1497,13 @@
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
       <c r="H55" s="6" t="str">
-        <v>Sp</v>
+        <v>Toughness</v>
       </c>
       <c r="I55" s="6" t="str">
-        <v>破魔(减对方魔防)</v>
+        <v>韧性(减对方幸运)</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="6"/>
@@ -1517,13 +1517,13 @@
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
       <c r="H56" s="6" t="str">
-        <v>Vampirism</v>
+        <v>Htarget</v>
       </c>
       <c r="I56" s="6" t="str">
-        <v>吸血(百分点,伤害转生命)</v>
+        <v>命中(减对方闪避)</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="6"/>
@@ -1537,13 +1537,13 @@
       <c r="F57" s="7"/>
       <c r="G57" s="7"/>
       <c r="H57" s="6" t="str">
-        <v>HpRegen</v>
+        <v>CritReduce</v>
       </c>
       <c r="I57" s="6" t="str">
-        <v>每秒回血</v>
+        <v>暴击抵抗</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="6"/>
@@ -1557,39 +1557,33 @@
       <c r="F58" s="7"/>
       <c r="G58" s="7"/>
       <c r="H58" s="6" t="str">
-        <v>MpRegen</v>
+        <v>Ar</v>
       </c>
       <c r="I58" s="6" t="str">
-        <v>每秒回蓝</v>
+        <v>破甲(减对方物防)</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="6"/>
     </row>
     <row r="59" ht="14" customHeight="1">
       <c r="A59" s="6"/>
-      <c r="B59" s="6" t="str">
-        <v>Attributes.AttributeModifierKind</v>
-      </c>
-      <c r="C59" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D59" s="8" t="b">
-        <v>1</v>
-      </c>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
       <c r="G59" s="7"/>
       <c r="H59" s="6" t="str">
-        <v>Flat</v>
+        <v>Sp</v>
       </c>
       <c r="I59" s="6" t="str">
-        <v>固定值</v>
+        <v>破魔(减对方魔防)</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="6"/>
@@ -1603,13 +1597,13 @@
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
       <c r="H60" s="6" t="str">
-        <v>PercentAdd</v>
+        <v>Vampirism</v>
       </c>
       <c r="I60" s="6" t="str">
-        <v>同类百分比相加</v>
+        <v>吸血(百分点,伤害转生命)</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="6"/>
@@ -1623,119 +1617,125 @@
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
       <c r="H61" s="6" t="str">
-        <v>PercentMult</v>
+        <v>HpRegen</v>
       </c>
       <c r="I61" s="6" t="str">
-        <v>独立百分比相乘</v>
+        <v>每秒回血</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="6"/>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="6"/>
-      <c r="B62" s="6" t="str">
-        <v>Equipment.EquipmentId</v>
-      </c>
-      <c r="C62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
       <c r="H62" s="6" t="str">
-        <v>None</v>
+        <v>MpRegen</v>
       </c>
       <c r="I62" s="6" t="str">
-        <v>无装备</v>
+        <v>每秒回蓝</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="K62" s="7"/>
       <c r="L62" s="6"/>
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
+      <c r="B63" s="6" t="str">
+        <v>Attributes.AttributeModifierKind</v>
+      </c>
+      <c r="C63" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D63" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
       <c r="H63" s="6" t="str">
-        <v>RoughPilgrimClothes</v>
+        <v>Flat</v>
       </c>
       <c r="I63" s="6" t="str">
-        <v>粗糙的行者服</v>
+        <v>固定值</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="K63" s="7"/>
       <c r="L63" s="6"/>
     </row>
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
       <c r="H64" s="6" t="str">
-        <v>RoughPilgrimStaff</v>
+        <v>PercentAdd</v>
       </c>
       <c r="I64" s="6" t="str">
-        <v>粗糙的行者棍</v>
+        <v>同类百分比相加</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K64" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="K64" s="7"/>
       <c r="L64" s="6"/>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
       <c r="H65" s="6" t="str">
-        <v>RoughCassock</v>
+        <v>PercentMult</v>
       </c>
       <c r="I65" s="6" t="str">
-        <v>粗糙的袈裟</v>
+        <v>独立百分比相乘</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K65" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="K65" s="7"/>
       <c r="L65" s="6"/>
     </row>
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
+      <c r="B66" s="6" t="str">
+        <v>Equipment.EquipmentId</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
       <c r="H66" s="6" t="str">
-        <v>RoughPineStaff</v>
+        <v>None</v>
       </c>
       <c r="I66" s="6" t="str">
-        <v>粗糙的松木杖</v>
+        <v>无装备</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
@@ -1749,13 +1749,13 @@
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
       <c r="H67" s="6" t="str">
-        <v>CommonPilgrimClothes</v>
+        <v>RoughPilgrimClothes</v>
       </c>
       <c r="I67" s="6" t="str">
-        <v>普通的行者服</v>
+        <v>粗糙的行者服</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
@@ -1769,13 +1769,13 @@
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
       <c r="H68" s="6" t="str">
-        <v>CommonPilgrimStaff</v>
+        <v>RoughPilgrimStaff</v>
       </c>
       <c r="I68" s="6" t="str">
-        <v>普通的行者棍</v>
+        <v>粗糙的行者棍</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
@@ -1789,13 +1789,13 @@
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6" t="str">
-        <v>CommonCassock</v>
+        <v>RoughCassock</v>
       </c>
       <c r="I69" s="6" t="str">
-        <v>普通的袈裟</v>
+        <v>粗糙的袈裟</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
@@ -1809,39 +1809,33 @@
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
       <c r="H70" s="6" t="str">
-        <v>CommonPineStaff</v>
+        <v>RoughPineStaff</v>
       </c>
       <c r="I70" s="6" t="str">
-        <v>普通的松木杖</v>
+        <v>粗糙的松木杖</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
     </row>
     <row r="71" ht="14" customHeight="1">
       <c r="A71" s="6"/>
-      <c r="B71" s="6" t="str">
-        <v>Equipment.EquipmentOwner</v>
-      </c>
-      <c r="C71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
       <c r="H71" s="6" t="str">
-        <v>Wukong</v>
+        <v>CommonPilgrimClothes</v>
       </c>
       <c r="I71" s="6" t="str">
-        <v>悟空</v>
+        <v>普通的行者服</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K71" s="6"/>
       <c r="L71" s="6"/>
@@ -1855,39 +1849,33 @@
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
       <c r="H72" s="6" t="str">
-        <v>Tangseng</v>
+        <v>CommonPilgrimStaff</v>
       </c>
       <c r="I72" s="6" t="str">
-        <v>唐僧</v>
+        <v>普通的行者棍</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="6"/>
-      <c r="B73" s="6" t="str">
-        <v>Equipment.EquipmentSlot</v>
-      </c>
-      <c r="C73" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
       <c r="H73" s="6" t="str">
-        <v>Weapon</v>
+        <v>CommonCassock</v>
       </c>
       <c r="I73" s="6" t="str">
-        <v>武器</v>
+        <v>普通的袈裟</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
@@ -1901,39 +1889,33 @@
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
       <c r="H74" s="6" t="str">
-        <v>Armor</v>
+        <v>CommonPineStaff</v>
       </c>
       <c r="I74" s="6" t="str">
-        <v>防具</v>
+        <v>普通的松木杖</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K74" s="6"/>
       <c r="L74" s="6"/>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="6"/>
-      <c r="B75" s="6" t="str">
-        <v>Equipment.EquipmentQuality</v>
-      </c>
-      <c r="C75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
       <c r="H75" s="6" t="str">
-        <v>Rough</v>
+        <v>EarthFiendRing</v>
       </c>
       <c r="I75" s="6" t="str">
-        <v>粗糙</v>
+        <v>地煞灵戒</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
@@ -1947,13 +1929,13 @@
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
       <c r="H76" s="6" t="str">
-        <v>Common</v>
+        <v>EarthFiendApeArmor</v>
       </c>
       <c r="I76" s="6" t="str">
-        <v>普通</v>
+        <v>地煞猿甲</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
@@ -1967,33 +1949,39 @@
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
       <c r="H77" s="6" t="str">
-        <v>Excellent</v>
+        <v>EarthFiendScepter</v>
       </c>
       <c r="I77" s="6" t="str">
-        <v>优秀</v>
+        <v>地煞权杖</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K77" s="6"/>
       <c r="L77" s="6"/>
     </row>
     <row r="78" ht="14" customHeight="1">
       <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
+      <c r="B78" s="6" t="str">
+        <v>Equipment.EquipmentOwner</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
       <c r="H78" s="6" t="str">
-        <v>Fine</v>
+        <v>Wukong</v>
       </c>
       <c r="I78" s="6" t="str">
-        <v>精良</v>
+        <v>悟空</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K78" s="6"/>
       <c r="L78" s="6"/>
@@ -2007,13 +1995,13 @@
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="6" t="str">
-        <v>Epic</v>
+        <v>Tangseng</v>
       </c>
       <c r="I79" s="6" t="str">
-        <v>史诗</v>
+        <v>唐僧</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
@@ -2027,38 +2015,36 @@
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
       <c r="H80" s="6" t="str">
-        <v>Legendary</v>
+        <v>Universal</v>
       </c>
       <c r="I80" s="6" t="str">
-        <v>传说</v>
+        <v>通用</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
     </row>
     <row r="81" ht="14" customHeight="1">
       <c r="A81" s="6"/>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>Loot.EquipmentDropPoolId</t>
-        </is>
-      </c>
-      <c r="C81" s="6">
-        <v>0</v>
-      </c>
-      <c r="D81" s="6">
+      <c r="B81" s="6" t="str">
+        <v>Equipment.EquipmentSlot</v>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
       <c r="H81" s="6" t="str">
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I81" s="6" t="str">
-        <v>不掉落</v>
+        <v>武器</v>
       </c>
       <c r="J81" s="6" t="n">
         <v>0</v>
@@ -2075,10 +2061,10 @@
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
       <c r="H82" s="6" t="str">
-        <v>Rough</v>
+        <v>Armor</v>
       </c>
       <c r="I82" s="6" t="str">
-        <v>粗糙装备</v>
+        <v>防具</v>
       </c>
       <c r="J82" s="6" t="n">
         <v>1</v>
@@ -2095,10 +2081,10 @@
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
       <c r="H83" s="6" t="str">
-        <v>Common</v>
+        <v>Accessory</v>
       </c>
       <c r="I83" s="6" t="str">
-        <v>普通装备</v>
+        <v>饰品</v>
       </c>
       <c r="J83" s="6" t="n">
         <v>2</v>
@@ -2109,7 +2095,7 @@
     <row r="84" ht="14" customHeight="1">
       <c r="A84" s="6"/>
       <c r="B84" s="6" t="str">
-        <v>Loot.PickupId</v>
+        <v>Equipment.EquipmentQuality</v>
       </c>
       <c r="C84" s="6" t="n">
         <v>0</v>
@@ -2121,9 +2107,11 @@
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
       <c r="H84" s="6" t="str">
-        <v>None</v>
-      </c>
-      <c r="I84" s="6"/>
+        <v>Rough</v>
+      </c>
+      <c r="I84" s="6" t="str">
+        <v>粗糙</v>
+      </c>
       <c r="J84" s="6" t="n">
         <v>0</v>
       </c>
@@ -2139,9 +2127,11 @@
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
       <c r="H85" s="6" t="str">
-        <v>SmallPeach</v>
-      </c>
-      <c r="I85" s="6"/>
+        <v>Common</v>
+      </c>
+      <c r="I85" s="6" t="str">
+        <v>普通</v>
+      </c>
       <c r="J85" s="6" t="n">
         <v>1</v>
       </c>
@@ -2157,9 +2147,11 @@
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
       <c r="H86" s="6" t="str">
-        <v>LargePeach</v>
-      </c>
-      <c r="I86" s="6"/>
+        <v>Excellent</v>
+      </c>
+      <c r="I86" s="6" t="str">
+        <v>优秀</v>
+      </c>
       <c r="J86" s="6" t="n">
         <v>2</v>
       </c>
@@ -2175,9 +2167,11 @@
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
       <c r="H87" s="6" t="str">
-        <v>ManaBottle</v>
-      </c>
-      <c r="I87" s="6"/>
+        <v>Fine</v>
+      </c>
+      <c r="I87" s="6" t="str">
+        <v>精良</v>
+      </c>
       <c r="J87" s="6" t="n">
         <v>3</v>
       </c>
@@ -2186,24 +2180,20 @@
     </row>
     <row r="88" ht="14" customHeight="1">
       <c r="A88" s="6"/>
-      <c r="B88" s="6" t="str">
-        <v>Loot.PickupEffect</v>
-      </c>
-      <c r="C88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
       <c r="H88" s="6" t="str">
-        <v>Health</v>
-      </c>
-      <c r="I88" s="6"/>
+        <v>Epic</v>
+      </c>
+      <c r="I88" s="6" t="str">
+        <v>史诗</v>
+      </c>
       <c r="J88" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
@@ -2217,37 +2207,41 @@
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
       <c r="H89" s="6" t="str">
-        <v>Mana</v>
-      </c>
-      <c r="I89" s="6"/>
+        <v>Legendary</v>
+      </c>
+      <c r="I89" s="6" t="str">
+        <v>传说</v>
+      </c>
       <c r="J89" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
     </row>
     <row r="90" ht="14" customHeight="1">
       <c r="A90" s="6"/>
-      <c r="B90" s="6" t="str">
-        <v>Skills.SkillHero</v>
-      </c>
-      <c r="C90" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D90" s="8" t="b">
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loot.EquipmentDropPoolId</t>
+        </is>
+      </c>
+      <c r="C90" s="6">
+        <v>0</v>
+      </c>
+      <c r="D90" s="6">
         <v>1</v>
       </c>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
       <c r="H90" s="6" t="str">
-        <v>Wukong</v>
+        <v>None</v>
       </c>
       <c r="I90" s="6" t="str">
-        <v>悟空</v>
+        <v>不掉落</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
@@ -2261,39 +2255,33 @@
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
       <c r="H91" s="6" t="str">
-        <v>Tangseng</v>
+        <v>Rough</v>
       </c>
       <c r="I91" s="6" t="str">
-        <v>唐僧</v>
+        <v>粗糙装备</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K91" s="6"/>
       <c r="L91" s="6"/>
     </row>
     <row r="92" ht="14" customHeight="1">
       <c r="A92" s="6"/>
-      <c r="B92" s="6" t="str">
-        <v>Skills.SkillId</v>
-      </c>
-      <c r="C92" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D92" s="8" t="b">
-        <v>1</v>
-      </c>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
       <c r="H92" s="6" t="str">
-        <v>RisingDragon</v>
+        <v>Common</v>
       </c>
       <c r="I92" s="6" t="str">
-        <v>升龙斩</v>
+        <v>普通装备</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="K92" s="6"/>
       <c r="L92" s="6"/>
@@ -2307,13 +2295,13 @@
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
       <c r="H93" s="6" t="str">
-        <v>FlameThrust</v>
+        <v>MacaqueKing</v>
       </c>
       <c r="I93" s="6" t="str">
-        <v>火炎突击</v>
+        <v>猕猴王装备</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="K93" s="6"/>
       <c r="L93" s="6"/>
@@ -2327,33 +2315,37 @@
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
       <c r="H94" s="6" t="str">
-        <v>BlazingFlash</v>
+        <v>TamarinKing</v>
       </c>
       <c r="I94" s="6" t="str">
-        <v>烈焰闪</v>
+        <v>禺狨王装备</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="K94" s="6"/>
       <c r="L94" s="6"/>
     </row>
     <row r="95" ht="14" customHeight="1">
       <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
+      <c r="B95" s="6" t="str">
+        <v>Loot.PickupId</v>
+      </c>
+      <c r="C95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
       <c r="H95" s="6" t="str">
-        <v>FlameStorm</v>
-      </c>
-      <c r="I95" s="6" t="str">
-        <v>烈焰风暴</v>
-      </c>
+        <v>None</v>
+      </c>
+      <c r="I95" s="6"/>
       <c r="J95" s="6" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="K95" s="6"/>
       <c r="L95" s="6"/>
@@ -2367,13 +2359,11 @@
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
       <c r="H96" s="6" t="str">
-        <v>FireDemonSlash</v>
-      </c>
-      <c r="I96" s="6" t="str">
-        <v>火魔斩</v>
-      </c>
+        <v>SmallPeach</v>
+      </c>
+      <c r="I96" s="6"/>
       <c r="J96" s="6" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
@@ -2387,13 +2377,11 @@
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
       <c r="H97" s="6" t="str">
-        <v>IceDragonWave</v>
-      </c>
-      <c r="I97" s="6" t="str">
-        <v>冰龙波</v>
-      </c>
+        <v>LargePeach</v>
+      </c>
+      <c r="I97" s="6"/>
       <c r="J97" s="6" t="n">
-        <v>201</v>
+        <v>2</v>
       </c>
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
@@ -2407,33 +2395,35 @@
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
       <c r="H98" s="6" t="str">
-        <v>DarkIceFormation</v>
-      </c>
-      <c r="I98" s="6" t="str">
-        <v>玄冰阵</v>
-      </c>
+        <v>ManaBottle</v>
+      </c>
+      <c r="I98" s="6"/>
       <c r="J98" s="6" t="n">
-        <v>202</v>
+        <v>3</v>
       </c>
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
     </row>
     <row r="99" ht="14" customHeight="1">
       <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
+      <c r="B99" s="6" t="str">
+        <v>Loot.PickupEffect</v>
+      </c>
+      <c r="C99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
       <c r="H99" s="6" t="str">
-        <v>WaterClone</v>
-      </c>
-      <c r="I99" s="6" t="str">
-        <v>水幻影</v>
-      </c>
+        <v>Health</v>
+      </c>
+      <c r="I99" s="6"/>
       <c r="J99" s="6" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
@@ -2447,79 +2437,83 @@
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
       <c r="H100" s="6" t="str">
-        <v>HeavenlyDew</v>
-      </c>
-      <c r="I100" s="6" t="str">
-        <v>天降甘露</v>
-      </c>
+        <v>Mana</v>
+      </c>
+      <c r="I100" s="6"/>
       <c r="J100" s="6" t="n">
-        <v>204</v>
+        <v>1</v>
       </c>
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
     </row>
     <row r="101" ht="14" customHeight="1">
       <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
+      <c r="B101" s="6" t="str">
+        <v>Skills.SkillHero</v>
+      </c>
+      <c r="C101" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D101" s="8" t="b">
+        <v>1</v>
+      </c>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
       <c r="H101" s="6" t="str">
-        <v>WaterDemonBurst</v>
+        <v>Wukong</v>
       </c>
       <c r="I101" s="6" t="str">
-        <v>水魔爆</v>
+        <v>悟空</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>205</v>
+        <v>1</v>
       </c>
       <c r="K101" s="6"/>
       <c r="L101" s="6"/>
     </row>
     <row r="102" ht="14" customHeight="1">
       <c r="A102" s="6"/>
-      <c r="B102" s="6" t="str">
-        <v>Skills.PassiveId</v>
-      </c>
-      <c r="C102" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D102" s="8" t="b">
-        <v>1</v>
-      </c>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
       <c r="H102" s="6" t="str">
-        <v>Vitality</v>
+        <v>Tangseng</v>
       </c>
       <c r="I102" s="6" t="str">
-        <v>热血</v>
+        <v>唐僧</v>
       </c>
       <c r="J102" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
     </row>
     <row r="103" ht="14" customHeight="1">
       <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
+      <c r="B103" s="6" t="str">
+        <v>Skills.SkillId</v>
+      </c>
+      <c r="C103" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D103" s="8" t="b">
+        <v>1</v>
+      </c>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
       <c r="G103" s="6"/>
       <c r="H103" s="6" t="str">
-        <v>ManaSpring</v>
+        <v>RisingDragon</v>
       </c>
       <c r="I103" s="6" t="str">
-        <v>魔泉</v>
+        <v>升龙斩</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
@@ -2533,13 +2527,13 @@
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
       <c r="H104" s="6" t="str">
-        <v>Frenzy</v>
+        <v>FlameThrust</v>
       </c>
       <c r="I104" s="6" t="str">
-        <v>狂暴</v>
+        <v>火炎突击</v>
       </c>
       <c r="J104" s="6" t="n">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="K104" s="6"/>
       <c r="L104" s="6"/>
@@ -2553,13 +2547,13 @@
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
       <c r="H105" s="6" t="str">
-        <v>EternalLight</v>
+        <v>BlazingFlash</v>
       </c>
       <c r="I105" s="6" t="str">
-        <v>光之永恒</v>
+        <v>烈焰闪</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>4</v>
+        <v>103</v>
       </c>
       <c r="K105" s="6"/>
       <c r="L105" s="6"/>
@@ -2573,39 +2567,33 @@
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
       <c r="H106" s="6" t="str">
-        <v>MoonBrilliance</v>
+        <v>FlameStorm</v>
       </c>
       <c r="I106" s="6" t="str">
-        <v>月之辉煌</v>
+        <v>烈焰风暴</v>
       </c>
       <c r="J106" s="6" t="n">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="K106" s="6"/>
       <c r="L106" s="6"/>
     </row>
     <row r="107" ht="14" customHeight="1">
       <c r="A107" s="6"/>
-      <c r="B107" s="6" t="str">
-        <v>Skills.PassiveEffect</v>
-      </c>
-      <c r="C107" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D107" s="8" t="b">
-        <v>1</v>
-      </c>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
       <c r="H107" s="6" t="str">
-        <v>MaxHealth</v>
+        <v>FireDemonSlash</v>
       </c>
       <c r="I107" s="6" t="str">
-        <v>生命上限</v>
+        <v>火魔斩</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K107" s="6"/>
       <c r="L107" s="6"/>
@@ -2619,13 +2607,13 @@
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
       <c r="H108" s="6" t="str">
-        <v>MaxMana</v>
+        <v>IceDragonWave</v>
       </c>
       <c r="I108" s="6" t="str">
-        <v>魔法上限</v>
+        <v>冰龙波</v>
       </c>
       <c r="J108" s="6" t="n">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="K108" s="6"/>
       <c r="L108" s="6"/>
@@ -2639,13 +2627,13 @@
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
       <c r="H109" s="6" t="str">
-        <v>CriticalChance</v>
+        <v>DarkIceFormation</v>
       </c>
       <c r="I109" s="6" t="str">
-        <v>暴击概率加成</v>
+        <v>玄冰阵</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>2</v>
+        <v>202</v>
       </c>
       <c r="K109" s="6"/>
       <c r="L109" s="6"/>
@@ -2659,13 +2647,13 @@
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
       <c r="H110" s="6" t="str">
-        <v>HealthRegen</v>
+        <v>WaterClone</v>
       </c>
       <c r="I110" s="6" t="str">
-        <v>每秒回血</v>
+        <v>水幻影</v>
       </c>
       <c r="J110" s="6" t="n">
-        <v>3</v>
+        <v>203</v>
       </c>
       <c r="K110" s="6"/>
       <c r="L110" s="6"/>
@@ -2679,59 +2667,59 @@
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
       <c r="H111" s="6" t="str">
-        <v>ManaRegen</v>
+        <v>HeavenlyDew</v>
       </c>
       <c r="I111" s="6" t="str">
-        <v>每秒回魔</v>
+        <v>天降甘露</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>4</v>
+        <v>204</v>
       </c>
       <c r="K111" s="6"/>
       <c r="L111" s="6"/>
     </row>
     <row r="112" ht="14" customHeight="1">
       <c r="A112" s="6"/>
-      <c r="B112" s="6" t="str">
-        <v>Skills.SkillHitId</v>
-      </c>
-      <c r="C112" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D112" s="8" t="b">
-        <v>1</v>
-      </c>
+      <c r="B112" s="6"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="6"/>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
       <c r="H112" s="6" t="str">
-        <v>None</v>
+        <v>WaterDemonBurst</v>
       </c>
       <c r="I112" s="6" t="str">
-        <v>无身体或特效伤害</v>
+        <v>水魔爆</v>
       </c>
       <c r="J112" s="6" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="K112" s="6"/>
       <c r="L112" s="6"/>
     </row>
     <row r="113" ht="14" customHeight="1">
       <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
+      <c r="B113" s="6" t="str">
+        <v>Skills.PassiveId</v>
+      </c>
+      <c r="C113" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D113" s="8" t="b">
+        <v>1</v>
+      </c>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
       <c r="H113" s="6" t="str">
-        <v>RisingDragon</v>
+        <v>Vitality</v>
       </c>
       <c r="I113" s="6" t="str">
-        <v>升龙斩</v>
+        <v>热血</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="K113" s="6"/>
       <c r="L113" s="6"/>
@@ -2745,13 +2733,13 @@
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
       <c r="H114" s="6" t="str">
-        <v>FlameThrust</v>
+        <v>ManaSpring</v>
       </c>
       <c r="I114" s="6" t="str">
-        <v>火炎突击</v>
+        <v>魔泉</v>
       </c>
       <c r="J114" s="6" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="K114" s="6"/>
       <c r="L114" s="6"/>
@@ -2765,13 +2753,13 @@
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
       <c r="H115" s="6" t="str">
-        <v>BlazingFlash</v>
+        <v>Frenzy</v>
       </c>
       <c r="I115" s="6" t="str">
-        <v>烈焰闪</v>
+        <v>狂暴</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="K115" s="6"/>
       <c r="L115" s="6"/>
@@ -2785,13 +2773,13 @@
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
       <c r="H116" s="6" t="str">
-        <v>FlameStorm</v>
+        <v>EternalLight</v>
       </c>
       <c r="I116" s="6" t="str">
-        <v>烈焰风暴</v>
+        <v>光之永恒</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="K116" s="6"/>
       <c r="L116" s="6"/>
@@ -2805,33 +2793,39 @@
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
       <c r="H117" s="6" t="str">
-        <v>FireDemonCombo</v>
+        <v>MoonBrilliance</v>
       </c>
       <c r="I117" s="6" t="str">
-        <v>火魔九连斩</v>
+        <v>月之辉煌</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>105</v>
+        <v>5</v>
       </c>
       <c r="K117" s="6"/>
       <c r="L117" s="6"/>
     </row>
     <row r="118" ht="14" customHeight="1">
       <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
-      <c r="C118" s="6"/>
-      <c r="D118" s="6"/>
+      <c r="B118" s="6" t="str">
+        <v>Skills.PassiveEffect</v>
+      </c>
+      <c r="C118" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D118" s="8" t="b">
+        <v>1</v>
+      </c>
       <c r="E118" s="6"/>
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
       <c r="H118" s="6" t="str">
-        <v>FireDemonDescent</v>
+        <v>MaxHealth</v>
       </c>
       <c r="I118" s="6" t="str">
-        <v>火魔下冲</v>
+        <v>生命上限</v>
       </c>
       <c r="J118" s="6" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="K118" s="6"/>
       <c r="L118" s="6"/>
@@ -2845,13 +2839,13 @@
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
       <c r="H119" s="6" t="str">
-        <v>FireDemonLanding</v>
+        <v>MaxMana</v>
       </c>
       <c r="I119" s="6" t="str">
-        <v>火魔落地斩</v>
+        <v>魔法上限</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="K119" s="6"/>
       <c r="L119" s="6"/>
@@ -2865,13 +2859,13 @@
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
       <c r="H120" s="6" t="str">
-        <v>IceDragonWave</v>
+        <v>CriticalChance</v>
       </c>
       <c r="I120" s="6" t="str">
-        <v>冰龙波</v>
+        <v>暴击概率加成</v>
       </c>
       <c r="J120" s="6" t="n">
-        <v>201</v>
+        <v>2</v>
       </c>
       <c r="K120" s="6"/>
       <c r="L120" s="6"/>
@@ -2885,13 +2879,13 @@
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
       <c r="H121" s="6" t="str">
-        <v>DarkIceFormation</v>
+        <v>HealthRegen</v>
       </c>
       <c r="I121" s="6" t="str">
-        <v>玄冰阵</v>
+        <v>每秒回血</v>
       </c>
       <c r="J121" s="6" t="n">
-        <v>202</v>
+        <v>3</v>
       </c>
       <c r="K121" s="6"/>
       <c r="L121" s="6"/>
@@ -2905,39 +2899,265 @@
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
       <c r="H122" s="6" t="str">
-        <v>WaterDemonPillar</v>
+        <v>ManaRegen</v>
       </c>
       <c r="I122" s="6" t="str">
-        <v>水魔光柱</v>
+        <v>每秒回魔</v>
       </c>
       <c r="J122" s="6" t="n">
-        <v>203</v>
+        <v>4</v>
       </c>
       <c r="K122" s="6"/>
       <c r="L122" s="6"/>
     </row>
     <row r="123" ht="14" customHeight="1">
       <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
-      <c r="C123" s="6"/>
-      <c r="D123" s="6"/>
+      <c r="B123" s="6" t="str">
+        <v>Skills.SkillHitId</v>
+      </c>
+      <c r="C123" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D123" s="8" t="b">
+        <v>1</v>
+      </c>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
       <c r="H123" s="6" t="str">
-        <v>WaterDemonFall</v>
+        <v>None</v>
       </c>
       <c r="I123" s="6" t="str">
-        <v>水魔追加下落</v>
+        <v>无身体或特效伤害</v>
       </c>
       <c r="J123" s="6" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="K123" s="6"/>
       <c r="L123" s="6"/>
     </row>
+    <row r="124">
+      <c r="A124" s="6"/>
+      <c r="B124" s="6"/>
+      <c r="C124" s="6"/>
+      <c r="D124" s="6"/>
+      <c r="E124" s="6"/>
+      <c r="F124" s="6"/>
+      <c r="G124" s="6"/>
+      <c r="H124" s="6" t="str">
+        <v>RisingDragon</v>
+      </c>
+      <c r="I124" s="6" t="str">
+        <v>升龙斩</v>
+      </c>
+      <c r="J124" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="K124" s="6"/>
+      <c r="L124" s="6"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="6"/>
+      <c r="B125" s="6"/>
+      <c r="C125" s="6"/>
+      <c r="D125" s="6"/>
+      <c r="E125" s="6"/>
+      <c r="F125" s="6"/>
+      <c r="G125" s="6"/>
+      <c r="H125" s="6" t="str">
+        <v>FlameThrust</v>
+      </c>
+      <c r="I125" s="6" t="str">
+        <v>火炎突击</v>
+      </c>
+      <c r="J125" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="K125" s="6"/>
+      <c r="L125" s="6"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="6"/>
+      <c r="B126" s="6"/>
+      <c r="C126" s="6"/>
+      <c r="D126" s="6"/>
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="6"/>
+      <c r="H126" s="6" t="str">
+        <v>BlazingFlash</v>
+      </c>
+      <c r="I126" s="6" t="str">
+        <v>烈焰闪</v>
+      </c>
+      <c r="J126" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="K126" s="6"/>
+      <c r="L126" s="6"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="6"/>
+      <c r="B127" s="6"/>
+      <c r="C127" s="6"/>
+      <c r="D127" s="6"/>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="6"/>
+      <c r="H127" s="6" t="str">
+        <v>FlameStorm</v>
+      </c>
+      <c r="I127" s="6" t="str">
+        <v>烈焰风暴</v>
+      </c>
+      <c r="J127" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="K127" s="6"/>
+      <c r="L127" s="6"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="6"/>
+      <c r="B128" s="6"/>
+      <c r="C128" s="6"/>
+      <c r="D128" s="6"/>
+      <c r="E128" s="6"/>
+      <c r="F128" s="6"/>
+      <c r="G128" s="6"/>
+      <c r="H128" s="6" t="str">
+        <v>FireDemonCombo</v>
+      </c>
+      <c r="I128" s="6" t="str">
+        <v>火魔九连斩</v>
+      </c>
+      <c r="J128" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="K128" s="6"/>
+      <c r="L128" s="6"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="6"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="6"/>
+      <c r="D129" s="6"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="6"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6" t="str">
+        <v>FireDemonDescent</v>
+      </c>
+      <c r="I129" s="6" t="str">
+        <v>火魔下冲</v>
+      </c>
+      <c r="J129" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="K129" s="6"/>
+      <c r="L129" s="6"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="6"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="6"/>
+      <c r="D130" s="6"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="6"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6" t="str">
+        <v>FireDemonLanding</v>
+      </c>
+      <c r="I130" s="6" t="str">
+        <v>火魔落地斩</v>
+      </c>
+      <c r="J130" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="K130" s="6"/>
+      <c r="L130" s="6"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="6"/>
+      <c r="B131" s="6"/>
+      <c r="C131" s="6"/>
+      <c r="D131" s="6"/>
+      <c r="E131" s="6"/>
+      <c r="F131" s="6"/>
+      <c r="G131" s="6"/>
+      <c r="H131" s="6" t="str">
+        <v>IceDragonWave</v>
+      </c>
+      <c r="I131" s="6" t="str">
+        <v>冰龙波</v>
+      </c>
+      <c r="J131" s="6" t="n">
+        <v>201</v>
+      </c>
+      <c r="K131" s="6"/>
+      <c r="L131" s="6"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="6"/>
+      <c r="B132" s="6"/>
+      <c r="C132" s="6"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="6"/>
+      <c r="H132" s="6" t="str">
+        <v>DarkIceFormation</v>
+      </c>
+      <c r="I132" s="6" t="str">
+        <v>玄冰阵</v>
+      </c>
+      <c r="J132" s="6" t="n">
+        <v>202</v>
+      </c>
+      <c r="K132" s="6"/>
+      <c r="L132" s="6"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="6"/>
+      <c r="B133" s="6"/>
+      <c r="C133" s="6"/>
+      <c r="D133" s="6"/>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6"/>
+      <c r="G133" s="6"/>
+      <c r="H133" s="6" t="str">
+        <v>WaterDemonPillar</v>
+      </c>
+      <c r="I133" s="6" t="str">
+        <v>水魔光柱</v>
+      </c>
+      <c r="J133" s="6" t="n">
+        <v>203</v>
+      </c>
+      <c r="K133" s="6"/>
+      <c r="L133" s="6"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="6"/>
+      <c r="B134" s="6"/>
+      <c r="C134" s="6"/>
+      <c r="D134" s="6"/>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="6"/>
+      <c r="H134" s="6" t="str">
+        <v>WaterDemonFall</v>
+      </c>
+      <c r="I134" s="6" t="str">
+        <v>水魔追加下落</v>
+      </c>
+      <c r="J134" s="6" t="n">
+        <v>204</v>
+      </c>
+      <c r="K134" s="6"/>
+      <c r="L134" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells>
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
